--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -237,6 +237,30 @@
   </si>
   <si>
     <t xml:space="preserve">Did some coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all well ends well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekend hoorah!!!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">did some research on tools </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired even after sleeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning da vinci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roaming market</t>
   </si>
 </sst>
 </file>
@@ -1541,180 +1565,372 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="12" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15" t="n">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J15" s="15" t="n">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="12" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I16" s="15" t="n">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J16" s="15" t="n">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="12" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>360</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="15" t="n">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="12" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15" t="n">
         <f aca="false">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J18" s="15" t="n">
         <f aca="false">IF(I18="","",1440-I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="12" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I19" s="15" t="n">
         <f aca="false">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <f aca="false">IF(I19="","",1440-I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="12" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I20" s="15" t="n">
         <f aca="false">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J20" s="15" t="n">
         <f aca="false">IF(I20="","",1440-I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="12" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15" t="n">
         <f aca="false">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J21" s="15" t="n">
         <f aca="false">IF(I21="","",1440-I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="12" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I22" s="15" t="n">
         <f aca="false">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J22" s="15" t="n">
         <f aca="false">IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -262,6 +262,42 @@
   <si>
     <t xml:space="preserve">roaming market</t>
   </si>
+  <si>
+    <t xml:space="preserve">tired very much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relaxed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early got up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">made some notes da vinci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hectic Monday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create project outline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very long day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good satisfied day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mechanically stuck but good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slept for recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tried from sleeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lazy Monday</t>
+  </si>
 </sst>
 </file>
 
@@ -272,7 +308,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,12 +423,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -463,7 +493,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -545,10 +575,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1560,7 +1586,7 @@
       <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="21" t="s">
+      <c r="N14" s="17" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1785,7 +1811,7 @@
         <v>63</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>55</v>
@@ -1933,293 +1959,605 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="12" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="15" t="n">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J23" s="15" t="n">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>410</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" s="15" t="n">
         <f aca="false">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J24" s="15" t="n">
         <f aca="false">IF(I24="","",1440-I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>460</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I25" s="15" t="n">
         <f aca="false">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J25" s="15" t="n">
         <f aca="false">IF(I25="","",1440-I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="12" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15" t="n">
         <f aca="false">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J26" s="15" t="n">
         <f aca="false">IF(I26="","",1440-I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="12" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I27" s="15" t="n">
         <f aca="false">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J27" s="15" t="n">
         <f aca="false">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>880</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="12" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15" t="n">
         <f aca="false">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J28" s="15" t="n">
         <f aca="false">IF(I28="","",1440-I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="12" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I29" s="15" t="n">
         <f aca="false">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J29" s="15" t="n">
         <f aca="false">IF(I29="","",1440-I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" s="15" t="n">
         <f aca="false">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J30" s="15" t="n">
         <f aca="false">IF(I30="","",1440-I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>370</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15" t="n">
         <f aca="false">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J31" s="15" t="n">
         <f aca="false">IF(I31="","",1440-I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="12" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I32" s="15" t="n">
         <f aca="false">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J32" s="15" t="n">
         <f aca="false">IF(I32="","",1440-I32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="12" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I33" s="15" t="n">
         <f aca="false">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J33" s="15" t="n">
         <f aca="false">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="12" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I34" s="15" t="n">
         <f aca="false">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J34" s="15" t="n">
         <f aca="false">IF(I34="","",1440-I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="12" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I35" s="15" t="n">
         <f aca="false">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J35" s="15" t="n">
         <f aca="false">IF(I35="","",1440-I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2241,7 +2579,7 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2263,7 +2601,7 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2285,7 +2623,7 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22"/>
+      <c r="A39" s="21"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2307,7 +2645,7 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="22"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2329,7 +2667,7 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2351,7 +2689,7 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="22"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2373,7 +2711,7 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2395,7 +2733,7 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="22"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2417,7 +2755,7 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -2439,7 +2777,7 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="22"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2461,7 +2799,7 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="22"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2483,7 +2821,7 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="22"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2505,7 +2843,7 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="22"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2527,7 +2865,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="22"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2549,7 +2887,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2571,7 +2909,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2593,7 +2931,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2615,7 +2953,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2637,7 +2975,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2659,7 +2997,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="22"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2681,7 +3019,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="22"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2703,7 +3041,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="22"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2725,7 +3063,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2747,7 +3085,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -2769,7 +3107,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="22"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -2791,7 +3129,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="22"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -2813,7 +3151,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="22"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -2835,7 +3173,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -2857,7 +3195,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2879,7 +3217,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22"/>
+      <c r="A66" s="21"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -2901,7 +3239,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="22"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -2923,7 +3261,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="22"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -2945,7 +3283,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -2967,7 +3305,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="22"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -2989,7 +3327,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="22"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3011,7 +3349,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="22"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3033,7 +3371,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="22"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3055,7 +3393,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="22"/>
+      <c r="A74" s="21"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3077,7 +3415,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="22"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3099,7 +3437,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="22"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3121,7 +3459,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="22"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3143,7 +3481,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="22"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3165,7 +3503,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="22"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3187,7 +3525,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="22"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3209,7 +3547,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="22"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3231,7 +3569,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="22"/>
+      <c r="A82" s="21"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3253,7 +3591,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="22"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3275,7 +3613,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="22"/>
+      <c r="A84" s="21"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3297,7 +3635,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="22"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3319,7 +3657,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="22"/>
+      <c r="A86" s="21"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3341,7 +3679,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="22"/>
+      <c r="A87" s="21"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3363,7 +3701,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="22"/>
+      <c r="A88" s="21"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3385,7 +3723,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="22"/>
+      <c r="A89" s="21"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3407,7 +3745,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="22"/>
+      <c r="A90" s="21"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3429,7 +3767,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="22"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3451,7 +3789,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="22"/>
+      <c r="A92" s="21"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -3473,7 +3811,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="22"/>
+      <c r="A93" s="21"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3495,7 +3833,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="22"/>
+      <c r="A94" s="21"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3517,7 +3855,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="22"/>
+      <c r="A95" s="21"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3539,7 +3877,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="22"/>
+      <c r="A96" s="21"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3561,7 +3899,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="22"/>
+      <c r="A97" s="21"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3583,7 +3921,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="22"/>
+      <c r="A98" s="21"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3605,7 +3943,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="22"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3627,7 +3965,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="22"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -3649,7 +3987,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="22"/>
+      <c r="A101" s="21"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -3671,7 +4009,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="22"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -3693,7 +4031,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="22"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -3715,7 +4053,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="22"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -3737,7 +4075,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="22"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -3759,7 +4097,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="22"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -3781,7 +4119,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="22"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -3803,7 +4141,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="22"/>
+      <c r="A108" s="21"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -3825,7 +4163,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="22"/>
+      <c r="A109" s="21"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -3847,7 +4185,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="22"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -3869,7 +4207,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="22"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -3891,7 +4229,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="22"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -3913,7 +4251,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="22"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -3935,7 +4273,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="22"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -3957,7 +4295,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="22"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -3979,7 +4317,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="22"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4001,7 +4339,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="22"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4023,7 +4361,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="22"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4045,7 +4383,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="22"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -4067,7 +4405,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="22"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -4089,7 +4427,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="22"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -4111,7 +4449,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="22"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -4133,7 +4471,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="22"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -4155,7 +4493,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="22"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -4177,7 +4515,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="22"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -4199,7 +4537,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="22"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4221,7 +4559,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="22"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4243,7 +4581,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="22"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4265,7 +4603,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="22"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4287,7 +4625,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="22"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4309,7 +4647,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="22"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4331,7 +4669,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="22"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4353,7 +4691,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="22"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4375,7 +4713,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="22"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -4397,7 +4735,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="22"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -4419,7 +4757,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="22"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -4441,7 +4779,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="22"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -4463,7 +4801,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="22"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4485,7 +4823,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="22"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4507,7 +4845,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="22"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4529,7 +4867,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="22"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4551,7 +4889,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="22"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4573,7 +4911,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="22"/>
+      <c r="A143" s="21"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4595,7 +4933,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="22"/>
+      <c r="A144" s="21"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4617,7 +4955,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="22"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4639,7 +4977,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="22"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4661,7 +4999,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="22"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -4683,7 +5021,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="22"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -4705,7 +5043,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="22"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -4727,7 +5065,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="22"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -4749,7 +5087,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="22"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -4771,7 +5109,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="22"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -4793,7 +5131,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="22"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -4815,7 +5153,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="22"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -4837,7 +5175,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="22"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -4859,7 +5197,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="22"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -4881,7 +5219,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="22"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -4903,7 +5241,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="22"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -4925,7 +5263,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="22"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -4947,7 +5285,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="22"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -4969,7 +5307,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="22"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -4991,7 +5329,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="22"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -5013,7 +5351,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="22"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -5035,7 +5373,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="22"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -5057,7 +5395,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="22"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -5079,7 +5417,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="22"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5101,7 +5439,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="22"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5123,7 +5461,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="22"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5145,7 +5483,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="22"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5167,7 +5505,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="22"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5189,7 +5527,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="22"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5211,7 +5549,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="22"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -5233,7 +5571,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="22"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5255,7 +5593,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="22"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5277,7 +5615,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="22"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5299,7 +5637,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="22"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5321,7 +5659,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="22"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5343,7 +5681,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="22"/>
+      <c r="A178" s="21"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5365,7 +5703,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="22"/>
+      <c r="A179" s="21"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5387,7 +5725,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="22"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5409,7 +5747,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="22"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5431,7 +5769,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="22"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5453,7 +5791,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="22"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5475,7 +5813,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="22"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5497,7 +5835,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="22"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5519,7 +5857,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="22"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5541,7 +5879,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="22"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5563,7 +5901,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="22"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5585,7 +5923,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="22"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5607,7 +5945,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="22"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5629,7 +5967,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="22"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5651,7 +5989,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="22"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -5673,7 +6011,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="22"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -5695,7 +6033,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="22"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -5717,7 +6055,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="22"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -5739,7 +6077,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="22"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -5761,7 +6099,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="22"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -5783,7 +6121,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="22"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -5805,7 +6143,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="22"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -5827,7 +6165,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="22"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -5849,7 +6187,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="22"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -5871,7 +6209,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="22"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -5893,7 +6231,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="22"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -5915,7 +6253,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="22"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -5937,7 +6275,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="22"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -5959,7 +6297,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="22"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -5981,7 +6319,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="22"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -6003,7 +6341,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="22"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -6025,7 +6363,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="22"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -6047,7 +6385,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="22"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -6069,7 +6407,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="22"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -6091,7 +6429,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="22"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -6113,7 +6451,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="22"/>
+      <c r="A213" s="21"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -6135,7 +6473,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="22"/>
+      <c r="A214" s="21"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -6157,7 +6495,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="22"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -6179,7 +6517,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="22"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -6201,7 +6539,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="22"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -6223,7 +6561,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="22"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -6245,7 +6583,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="22"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6267,7 +6605,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="22"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6289,7 +6627,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="22"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6311,7 +6649,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="22"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -6333,7 +6671,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="22"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -6355,7 +6693,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="22"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -6377,7 +6715,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="22"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -6399,7 +6737,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="22"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6421,7 +6759,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="22"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6443,7 +6781,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="22"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -6465,7 +6803,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="22"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -6487,7 +6825,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="22"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -6509,7 +6847,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="22"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -6531,7 +6869,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="22"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -6553,7 +6891,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="22"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -6575,7 +6913,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="22"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -6597,7 +6935,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="22"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -6619,7 +6957,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="22"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -6641,7 +6979,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="22"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -6663,7 +7001,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="22"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -6685,7 +7023,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="22"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -6707,7 +7045,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="22"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -6729,7 +7067,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="22"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -6751,7 +7089,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="22"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -6773,7 +7111,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="22"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -6795,7 +7133,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="22"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -6817,7 +7155,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="22"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -6839,7 +7177,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="22"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -6861,7 +7199,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="22"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -6883,7 +7221,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="22"/>
+      <c r="A248" s="21"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -6905,7 +7243,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="22"/>
+      <c r="A249" s="21"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -6927,7 +7265,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="22"/>
+      <c r="A250" s="21"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -6949,7 +7287,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="22"/>
+      <c r="A251" s="21"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -6971,7 +7309,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="22"/>
+      <c r="A252" s="21"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -6993,7 +7331,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="22"/>
+      <c r="A253" s="21"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -7015,7 +7353,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="22"/>
+      <c r="A254" s="21"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -7037,7 +7375,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="22"/>
+      <c r="A255" s="21"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -7059,7 +7397,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="22"/>
+      <c r="A256" s="21"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -7081,7 +7419,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="22"/>
+      <c r="A257" s="21"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -7103,7 +7441,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="22"/>
+      <c r="A258" s="21"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -7125,7 +7463,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="22"/>
+      <c r="A259" s="21"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -7147,7 +7485,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="22"/>
+      <c r="A260" s="21"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -7169,7 +7507,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="22"/>
+      <c r="A261" s="21"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -7191,7 +7529,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="22"/>
+      <c r="A262" s="21"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -7213,7 +7551,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="22"/>
+      <c r="A263" s="21"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -7235,7 +7573,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="22"/>
+      <c r="A264" s="21"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -7257,7 +7595,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="22"/>
+      <c r="A265" s="21"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7279,7 +7617,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="22"/>
+      <c r="A266" s="21"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7301,7 +7639,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="22"/>
+      <c r="A267" s="21"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7323,7 +7661,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="22"/>
+      <c r="A268" s="21"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -7345,7 +7683,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="22"/>
+      <c r="A269" s="21"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -7367,7 +7705,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="22"/>
+      <c r="A270" s="21"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -7389,7 +7727,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="22"/>
+      <c r="A271" s="21"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -7411,7 +7749,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="22"/>
+      <c r="A272" s="21"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -7433,7 +7771,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="22"/>
+      <c r="A273" s="21"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -7455,7 +7793,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="22"/>
+      <c r="A274" s="21"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -7477,7 +7815,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="22"/>
+      <c r="A275" s="21"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -7499,7 +7837,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="22"/>
+      <c r="A276" s="21"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -7521,7 +7859,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="22"/>
+      <c r="A277" s="21"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -7543,7 +7881,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="22"/>
+      <c r="A278" s="21"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -7565,7 +7903,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="22"/>
+      <c r="A279" s="21"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -7587,7 +7925,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="22"/>
+      <c r="A280" s="21"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -7609,7 +7947,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="22"/>
+      <c r="A281" s="21"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -7631,7 +7969,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="22"/>
+      <c r="A282" s="21"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -7653,7 +7991,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="22"/>
+      <c r="A283" s="21"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -7675,7 +8013,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="22"/>
+      <c r="A284" s="21"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -7697,7 +8035,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="22"/>
+      <c r="A285" s="21"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -7719,7 +8057,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="22"/>
+      <c r="A286" s="21"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -7741,7 +8079,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="22"/>
+      <c r="A287" s="21"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -7763,7 +8101,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="22"/>
+      <c r="A288" s="21"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -7785,7 +8123,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="22"/>
+      <c r="A289" s="21"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -7807,7 +8145,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="22"/>
+      <c r="A290" s="21"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -7829,7 +8167,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="22"/>
+      <c r="A291" s="21"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -7851,7 +8189,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="22"/>
+      <c r="A292" s="21"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -7873,7 +8211,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="22"/>
+      <c r="A293" s="21"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -7895,7 +8233,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="22"/>
+      <c r="A294" s="21"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -7917,7 +8255,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="22"/>
+      <c r="A295" s="21"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -7939,7 +8277,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="22"/>
+      <c r="A296" s="21"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -7961,7 +8299,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="22"/>
+      <c r="A297" s="21"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -7983,7 +8321,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="22"/>
+      <c r="A298" s="21"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -8005,7 +8343,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="22"/>
+      <c r="A299" s="21"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -8027,7 +8365,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="22"/>
+      <c r="A300" s="21"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -8049,7 +8387,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="22"/>
+      <c r="A301" s="21"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -8071,7 +8409,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="22"/>
+      <c r="A302" s="21"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -8093,7 +8431,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="22"/>
+      <c r="A303" s="21"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -8115,7 +8453,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="22"/>
+      <c r="A304" s="21"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -8137,7 +8475,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="22"/>
+      <c r="A305" s="21"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -8159,7 +8497,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="22"/>
+      <c r="A306" s="21"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -8181,7 +8519,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="22"/>
+      <c r="A307" s="21"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -8203,7 +8541,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="22"/>
+      <c r="A308" s="21"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -8225,7 +8563,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="22"/>
+      <c r="A309" s="21"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -8247,7 +8585,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="22"/>
+      <c r="A310" s="21"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8269,7 +8607,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="22"/>
+      <c r="A311" s="21"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -8291,7 +8629,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="22"/>
+      <c r="A312" s="21"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -8313,7 +8651,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="22"/>
+      <c r="A313" s="21"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -8335,7 +8673,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="22"/>
+      <c r="A314" s="21"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -8357,7 +8695,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="22"/>
+      <c r="A315" s="21"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -8379,7 +8717,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="22"/>
+      <c r="A316" s="21"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -8401,7 +8739,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="22"/>
+      <c r="A317" s="21"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -8423,7 +8761,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="22"/>
+      <c r="A318" s="21"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -8445,7 +8783,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="22"/>
+      <c r="A319" s="21"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -8467,7 +8805,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="22"/>
+      <c r="A320" s="21"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -8489,7 +8827,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="22"/>
+      <c r="A321" s="21"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -8511,7 +8849,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="22"/>
+      <c r="A322" s="21"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -8533,7 +8871,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="22"/>
+      <c r="A323" s="21"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -8555,7 +8893,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="22"/>
+      <c r="A324" s="21"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -8577,7 +8915,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="22"/>
+      <c r="A325" s="21"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -8599,7 +8937,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="22"/>
+      <c r="A326" s="21"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -8621,7 +8959,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="22"/>
+      <c r="A327" s="21"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -8643,7 +8981,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="22"/>
+      <c r="A328" s="21"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -8665,7 +9003,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="22"/>
+      <c r="A329" s="21"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -8687,7 +9025,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="22"/>
+      <c r="A330" s="21"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -8709,7 +9047,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="22"/>
+      <c r="A331" s="21"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -8731,7 +9069,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="22"/>
+      <c r="A332" s="21"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -8753,7 +9091,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="22"/>
+      <c r="A333" s="21"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -8775,7 +9113,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="22"/>
+      <c r="A334" s="21"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -8797,7 +9135,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="22"/>
+      <c r="A335" s="21"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -8819,7 +9157,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="22"/>
+      <c r="A336" s="21"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -8841,7 +9179,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="22"/>
+      <c r="A337" s="21"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -8863,7 +9201,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="22"/>
+      <c r="A338" s="21"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -8885,7 +9223,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="22"/>
+      <c r="A339" s="21"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -8907,7 +9245,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="22"/>
+      <c r="A340" s="21"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -8929,7 +9267,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="22"/>
+      <c r="A341" s="21"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -8951,7 +9289,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="22"/>
+      <c r="A342" s="21"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -8973,7 +9311,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="22"/>
+      <c r="A343" s="21"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -8995,7 +9333,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="22"/>
+      <c r="A344" s="21"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -9017,7 +9355,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="22"/>
+      <c r="A345" s="21"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -9039,7 +9377,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="22"/>
+      <c r="A346" s="21"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -9061,7 +9399,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="22"/>
+      <c r="A347" s="21"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -9083,7 +9421,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="22"/>
+      <c r="A348" s="21"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -9105,7 +9443,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="22"/>
+      <c r="A349" s="21"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -9127,7 +9465,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="22"/>
+      <c r="A350" s="21"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -9149,7 +9487,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="22"/>
+      <c r="A351" s="21"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -9171,7 +9509,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="22"/>
+      <c r="A352" s="21"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -9193,7 +9531,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="22"/>
+      <c r="A353" s="21"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -9215,7 +9553,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="22"/>
+      <c r="A354" s="21"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -9237,7 +9575,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="22"/>
+      <c r="A355" s="21"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -9259,7 +9597,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="22"/>
+      <c r="A356" s="21"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -9281,7 +9619,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="22"/>
+      <c r="A357" s="21"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -9303,7 +9641,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="22"/>
+      <c r="A358" s="21"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -9325,7 +9663,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="22"/>
+      <c r="A359" s="21"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -9347,7 +9685,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="22"/>
+      <c r="A360" s="21"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -9369,7 +9707,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="22"/>
+      <c r="A361" s="21"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -9391,7 +9729,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="22"/>
+      <c r="A362" s="21"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -9413,7 +9751,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="22"/>
+      <c r="A363" s="21"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -9435,7 +9773,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="22"/>
+      <c r="A364" s="21"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -9457,7 +9795,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="22"/>
+      <c r="A365" s="21"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -9479,7 +9817,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="22"/>
+      <c r="A366" s="21"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -9501,7 +9839,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="22"/>
+      <c r="A367" s="21"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -9523,7 +9861,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="22"/>
+      <c r="A368" s="21"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -9545,7 +9883,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="22"/>
+      <c r="A369" s="21"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -9567,7 +9905,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="22"/>
+      <c r="A370" s="21"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -9589,7 +9927,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="22"/>
+      <c r="A371" s="21"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -9611,7 +9949,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="22"/>
+      <c r="A372" s="21"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -9633,7 +9971,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="22"/>
+      <c r="A373" s="21"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -9655,7 +9993,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="22"/>
+      <c r="A374" s="21"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -9677,7 +10015,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="22"/>
+      <c r="A375" s="21"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -9699,7 +10037,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="22"/>
+      <c r="A376" s="21"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -9721,7 +10059,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="22"/>
+      <c r="A377" s="21"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -9743,7 +10081,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="22"/>
+      <c r="A378" s="21"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -9765,7 +10103,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="22"/>
+      <c r="A379" s="21"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -9787,7 +10125,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="22"/>
+      <c r="A380" s="21"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -9809,7 +10147,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="22"/>
+      <c r="A381" s="21"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -9831,7 +10169,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="22"/>
+      <c r="A382" s="21"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -9853,7 +10191,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="22"/>
+      <c r="A383" s="21"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -9875,7 +10213,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="22"/>
+      <c r="A384" s="21"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -9897,7 +10235,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="22"/>
+      <c r="A385" s="21"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -9919,7 +10257,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="22"/>
+      <c r="A386" s="21"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -9941,7 +10279,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="22"/>
+      <c r="A387" s="21"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -9963,7 +10301,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="22"/>
+      <c r="A388" s="21"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -9985,7 +10323,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="22"/>
+      <c r="A389" s="21"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -10007,7 +10345,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="22"/>
+      <c r="A390" s="21"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -10029,7 +10367,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="22"/>
+      <c r="A391" s="21"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -10051,7 +10389,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="22"/>
+      <c r="A392" s="21"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -10073,7 +10411,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="22"/>
+      <c r="A393" s="21"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -10095,7 +10433,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="22"/>
+      <c r="A394" s="21"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -10117,7 +10455,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="22"/>
+      <c r="A395" s="21"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -10139,7 +10477,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="22"/>
+      <c r="A396" s="21"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -10161,7 +10499,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="22"/>
+      <c r="A397" s="21"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -10183,7 +10521,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="22"/>
+      <c r="A398" s="21"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -10205,7 +10543,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="22"/>
+      <c r="A399" s="21"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -10227,7 +10565,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="22"/>
+      <c r="A400" s="21"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -10249,7 +10587,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="22"/>
+      <c r="A401" s="21"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>
@@ -10284,16 +10622,28 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K401" type="list">
+  <dataValidations count="6">
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K22 K36:K401" type="list">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L22 L36:L401" type="list">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M22 M36:M401" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="equal" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K23:K35" type="list">
+      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L23:L35" type="list">
+      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M23:M35" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -192,111 +192,6 @@
   </si>
   <si>
     <t xml:space="preserve">Today 66 day completed at ihub.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satisfied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first day at the university </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well and good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hectic  DAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsatisfied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not that boring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stressed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">travelled back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visited temple with friends </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Came back by evening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did some coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all well ends well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">very tired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">satisfied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weekend hoorah!!!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">did some research on tools </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tired even after sleeping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">learning da vinci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roaming market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tired very much</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relaxed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">early got up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">made some notes da vinci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hectic Monday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create project outline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">very long day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">good satisfied day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mechanically stuck but good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slept for recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tried from sleeping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lazy Monday</t>
   </si>
 </sst>
 </file>
@@ -493,7 +388,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -563,18 +458,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1223,1341 +1106,645 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>410</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="18" t="n">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15" t="str">
         <f aca="false">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v>915</v>
-      </c>
-      <c r="J7" s="18" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="15" t="str">
         <f aca="false">IF(I7="","",1440-I7)</f>
-        <v>525</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="20" t="s">
-        <v>60</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I8" s="15" t="n">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15" t="str">
         <f aca="false">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v>840</v>
-      </c>
-      <c r="J8" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="15" t="str">
         <f aca="false">IF(I8="","",1440-I8)</f>
-        <v>600</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="15" t="n">
+      <c r="A9" s="18"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15" t="str">
         <f aca="false">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v>1050</v>
-      </c>
-      <c r="J9" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="15" t="str">
         <f aca="false">IF(I9="","",1440-I9)</f>
-        <v>390</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>64</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>360</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I10" s="15" t="n">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15" t="str">
         <f aca="false">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v>780</v>
-      </c>
-      <c r="J10" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="15" t="str">
         <f aca="false">IF(I10="","",1440-I10)</f>
-        <v>660</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>66</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>150</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" s="15" t="n">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15" t="str">
         <f aca="false">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v>760</v>
-      </c>
-      <c r="J11" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J11" s="15" t="str">
         <f aca="false">IF(I11="","",1440-I11)</f>
-        <v>680</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>68</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>340</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="I12" s="15" t="n">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15" t="str">
         <f aca="false">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v>690</v>
-      </c>
-      <c r="J12" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="15" t="str">
         <f aca="false">IF(I12="","",1440-I12)</f>
-        <v>750</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>410</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="I13" s="15" t="n">
+      <c r="A13" s="18"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15" t="str">
         <f aca="false">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>630</v>
-      </c>
-      <c r="J13" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="15" t="str">
         <f aca="false">IF(I13="","",1440-I13)</f>
-        <v>810</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>70</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="I14" s="15" t="n">
+      <c r="A14" s="18"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15" t="str">
         <f aca="false">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v>960</v>
-      </c>
-      <c r="J14" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J14" s="15" t="str">
         <f aca="false">IF(I14="","",1440-I14)</f>
-        <v>480</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>71</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I15" s="15" t="n">
+      <c r="A15" s="18"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15" t="str">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v>880</v>
-      </c>
-      <c r="J15" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J15" s="15" t="str">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v>560</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>72</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I16" s="15" t="n">
+      <c r="A16" s="18"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15" t="str">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v>1025</v>
-      </c>
-      <c r="J16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="15" t="str">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v>415</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>73</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>360</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="I17" s="15" t="n">
+      <c r="A17" s="18"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15" t="str">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v>820</v>
-      </c>
-      <c r="J17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J17" s="15" t="str">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v>620</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I18" s="15" t="n">
+      <c r="A18" s="18"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15" t="str">
         <f aca="false">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v>930</v>
-      </c>
-      <c r="J18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="15" t="str">
         <f aca="false">IF(I18="","",1440-I18)</f>
-        <v>510</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>75</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I19" s="15" t="n">
+      <c r="A19" s="18"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15" t="str">
         <f aca="false">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v>780</v>
-      </c>
-      <c r="J19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="15" t="str">
         <f aca="false">IF(I19="","",1440-I19)</f>
-        <v>660</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="I20" s="15" t="n">
+      <c r="A20" s="18"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15" t="str">
         <f aca="false">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v>730</v>
-      </c>
-      <c r="J20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J20" s="15" t="str">
         <f aca="false">IF(I20="","",1440-I20)</f>
-        <v>710</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>77</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="I21" s="15" t="n">
+      <c r="A21" s="18"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="str">
         <f aca="false">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v>1010</v>
-      </c>
-      <c r="J21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J21" s="15" t="str">
         <f aca="false">IF(I21="","",1440-I21)</f>
-        <v>430</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>78</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B22" s="14" t="n">
-        <v>380</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="I22" s="15" t="n">
+      <c r="A22" s="18"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15" t="str">
         <f aca="false">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v>800</v>
-      </c>
-      <c r="J22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str">
         <f aca="false">IF(I22="","",1440-I22)</f>
-        <v>640</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>79</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>360</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I23" s="15" t="n">
+      <c r="A23" s="18"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15" t="str">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v>950</v>
-      </c>
-      <c r="J23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v>490</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>80</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>410</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I24" s="15" t="n">
+      <c r="A24" s="18"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15" t="str">
         <f aca="false">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v>800</v>
-      </c>
-      <c r="J24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str">
         <f aca="false">IF(I24="","",1440-I24)</f>
-        <v>640</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>81</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>460</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I25" s="15" t="n">
+      <c r="A25" s="18"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15" t="str">
         <f aca="false">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v>880</v>
-      </c>
-      <c r="J25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
         <f aca="false">IF(I25="","",1440-I25)</f>
-        <v>560</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>82</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>480</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="15" t="n">
+      <c r="A26" s="18"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15" t="str">
         <f aca="false">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v>740</v>
-      </c>
-      <c r="J26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
         <f aca="false">IF(I26="","",1440-I26)</f>
-        <v>700</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>83</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="I27" s="15" t="n">
+      <c r="A27" s="18"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15" t="str">
         <f aca="false">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v>560</v>
-      </c>
-      <c r="J27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="15" t="str">
         <f aca="false">IF(I27="","",1440-I27)</f>
-        <v>880</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>70</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>410</v>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I28" s="15" t="n">
+      <c r="A28" s="18"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15" t="str">
         <f aca="false">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v>965</v>
-      </c>
-      <c r="J28" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="15" t="str">
         <f aca="false">IF(I28="","",1440-I28)</f>
-        <v>475</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>84</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>390</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="I29" s="15" t="n">
+      <c r="A29" s="18"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15" t="str">
         <f aca="false">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-        <v>880</v>
-      </c>
-      <c r="J29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="15" t="str">
         <f aca="false">IF(I29="","",1440-I29)</f>
-        <v>560</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>85</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>420</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="I30" s="15" t="n">
+      <c r="A30" s="18"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15" t="str">
         <f aca="false">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v>1090</v>
-      </c>
-      <c r="J30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="15" t="str">
         <f aca="false">IF(I30="","",1440-I30)</f>
-        <v>350</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>86</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>370</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="I31" s="15" t="n">
+      <c r="A31" s="18"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15" t="str">
         <f aca="false">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v>880</v>
-      </c>
-      <c r="J31" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="15" t="str">
         <f aca="false">IF(I31="","",1440-I31)</f>
-        <v>560</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>87</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>390</v>
-      </c>
-      <c r="C32" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="I32" s="15" t="n">
+      <c r="A32" s="18"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15" t="str">
         <f aca="false">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v>940</v>
-      </c>
-      <c r="J32" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="15" t="str">
         <f aca="false">IF(I32="","",1440-I32)</f>
-        <v>500</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>88</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>410</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" s="15" t="n">
+      <c r="A33" s="18"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15" t="str">
         <f aca="false">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v>650</v>
-      </c>
-      <c r="J33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="15" t="str">
         <f aca="false">IF(I33="","",1440-I33)</f>
-        <v>790</v>
-      </c>
-      <c r="K33" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>89</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B34" s="14" t="n">
-        <v>390</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="I34" s="15" t="n">
+      <c r="A34" s="18"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15" t="str">
         <f aca="false">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
-        <v>640</v>
-      </c>
-      <c r="J34" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="15" t="str">
         <f aca="false">IF(I34="","",1440-I34)</f>
-        <v>800</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>90</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B35" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="I35" s="15" t="n">
+      <c r="A35" s="18"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15" t="str">
         <f aca="false">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v>840</v>
-      </c>
-      <c r="J35" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="15" t="str">
         <f aca="false">IF(I35="","",1440-I35)</f>
-        <v>600</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M35" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>91</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2579,7 +1766,7 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2601,7 +1788,7 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2623,7 +1810,7 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21"/>
+      <c r="A39" s="18"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2645,7 +1832,7 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -2667,7 +1854,7 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21"/>
+      <c r="A41" s="18"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -2689,7 +1876,7 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -2711,7 +1898,7 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2733,7 +1920,7 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -2755,7 +1942,7 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -2777,7 +1964,7 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2799,7 +1986,7 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2821,7 +2008,7 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2843,7 +2030,7 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21"/>
+      <c r="A49" s="18"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2865,7 +2052,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2887,7 +2074,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21"/>
+      <c r="A51" s="18"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2909,7 +2096,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21"/>
+      <c r="A52" s="18"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2931,7 +2118,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2953,7 +2140,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2975,7 +2162,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2997,7 +2184,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3019,7 +2206,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -3041,7 +2228,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -3063,7 +2250,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
+      <c r="A59" s="18"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -3085,7 +2272,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3107,7 +2294,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="21"/>
+      <c r="A61" s="18"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3129,7 +2316,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21"/>
+      <c r="A62" s="18"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3151,7 +2338,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21"/>
+      <c r="A63" s="18"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3173,7 +2360,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21"/>
+      <c r="A64" s="18"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3195,7 +2382,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21"/>
+      <c r="A65" s="18"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3217,7 +2404,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21"/>
+      <c r="A66" s="18"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3239,7 +2426,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3261,7 +2448,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3283,7 +2470,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3305,7 +2492,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="21"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3327,7 +2514,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="21"/>
+      <c r="A71" s="18"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3349,7 +2536,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21"/>
+      <c r="A72" s="18"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3371,7 +2558,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
+      <c r="A73" s="18"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3393,7 +2580,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21"/>
+      <c r="A74" s="18"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3415,7 +2602,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="21"/>
+      <c r="A75" s="18"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3437,7 +2624,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="21"/>
+      <c r="A76" s="18"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3459,7 +2646,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="21"/>
+      <c r="A77" s="18"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3481,7 +2668,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="21"/>
+      <c r="A78" s="18"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3503,7 +2690,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="21"/>
+      <c r="A79" s="18"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3525,7 +2712,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="21"/>
+      <c r="A80" s="18"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3547,7 +2734,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21"/>
+      <c r="A81" s="18"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3569,7 +2756,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21"/>
+      <c r="A82" s="18"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3591,7 +2778,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21"/>
+      <c r="A83" s="18"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3613,7 +2800,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="21"/>
+      <c r="A84" s="18"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3635,7 +2822,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="21"/>
+      <c r="A85" s="18"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3657,7 +2844,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21"/>
+      <c r="A86" s="18"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3679,7 +2866,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21"/>
+      <c r="A87" s="18"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3701,7 +2888,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="21"/>
+      <c r="A88" s="18"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3723,7 +2910,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="21"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3745,7 +2932,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="21"/>
+      <c r="A90" s="18"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3767,7 +2954,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="21"/>
+      <c r="A91" s="18"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3789,7 +2976,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="21"/>
+      <c r="A92" s="18"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -3811,7 +2998,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="21"/>
+      <c r="A93" s="18"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3833,7 +3020,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="21"/>
+      <c r="A94" s="18"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3855,7 +3042,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="21"/>
+      <c r="A95" s="18"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3877,7 +3064,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="21"/>
+      <c r="A96" s="18"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3899,7 +3086,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="21"/>
+      <c r="A97" s="18"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3921,7 +3108,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="21"/>
+      <c r="A98" s="18"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3943,7 +3130,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="21"/>
+      <c r="A99" s="18"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3965,7 +3152,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="21"/>
+      <c r="A100" s="18"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -3987,7 +3174,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="21"/>
+      <c r="A101" s="18"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -4009,7 +3196,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="21"/>
+      <c r="A102" s="18"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -4031,7 +3218,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="21"/>
+      <c r="A103" s="18"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -4053,7 +3240,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="21"/>
+      <c r="A104" s="18"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -4075,7 +3262,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="21"/>
+      <c r="A105" s="18"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -4097,7 +3284,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="21"/>
+      <c r="A106" s="18"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -4119,7 +3306,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="21"/>
+      <c r="A107" s="18"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -4141,7 +3328,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="21"/>
+      <c r="A108" s="18"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -4163,7 +3350,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="21"/>
+      <c r="A109" s="18"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -4185,7 +3372,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="21"/>
+      <c r="A110" s="18"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -4207,7 +3394,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="21"/>
+      <c r="A111" s="18"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -4229,7 +3416,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="21"/>
+      <c r="A112" s="18"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -4251,7 +3438,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="21"/>
+      <c r="A113" s="18"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -4273,7 +3460,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="21"/>
+      <c r="A114" s="18"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -4295,7 +3482,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="21"/>
+      <c r="A115" s="18"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4317,7 +3504,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="21"/>
+      <c r="A116" s="18"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4339,7 +3526,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="21"/>
+      <c r="A117" s="18"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4361,7 +3548,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="21"/>
+      <c r="A118" s="18"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4383,7 +3570,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="21"/>
+      <c r="A119" s="18"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -4405,7 +3592,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="21"/>
+      <c r="A120" s="18"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -4427,7 +3614,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="21"/>
+      <c r="A121" s="18"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -4449,7 +3636,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="21"/>
+      <c r="A122" s="18"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -4471,7 +3658,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="21"/>
+      <c r="A123" s="18"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -4493,7 +3680,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="21"/>
+      <c r="A124" s="18"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -4515,7 +3702,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="21"/>
+      <c r="A125" s="18"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -4537,7 +3724,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="21"/>
+      <c r="A126" s="18"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4559,7 +3746,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="21"/>
+      <c r="A127" s="18"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4581,7 +3768,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="21"/>
+      <c r="A128" s="18"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4603,7 +3790,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="21"/>
+      <c r="A129" s="18"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4625,7 +3812,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="21"/>
+      <c r="A130" s="18"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4647,7 +3834,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="21"/>
+      <c r="A131" s="18"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4669,7 +3856,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="21"/>
+      <c r="A132" s="18"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4691,7 +3878,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="21"/>
+      <c r="A133" s="18"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4713,7 +3900,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="21"/>
+      <c r="A134" s="18"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -4735,7 +3922,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="21"/>
+      <c r="A135" s="18"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -4757,7 +3944,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="21"/>
+      <c r="A136" s="18"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -4779,7 +3966,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="21"/>
+      <c r="A137" s="18"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -4801,7 +3988,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="21"/>
+      <c r="A138" s="18"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4823,7 +4010,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="21"/>
+      <c r="A139" s="18"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4845,7 +4032,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="21"/>
+      <c r="A140" s="18"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4867,7 +4054,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="21"/>
+      <c r="A141" s="18"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4889,7 +4076,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="21"/>
+      <c r="A142" s="18"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4911,7 +4098,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="21"/>
+      <c r="A143" s="18"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4933,7 +4120,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="21"/>
+      <c r="A144" s="18"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4955,7 +4142,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="21"/>
+      <c r="A145" s="18"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4977,7 +4164,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="21"/>
+      <c r="A146" s="18"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4999,7 +4186,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="21"/>
+      <c r="A147" s="18"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -5021,7 +4208,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="21"/>
+      <c r="A148" s="18"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -5043,7 +4230,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="21"/>
+      <c r="A149" s="18"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -5065,7 +4252,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="21"/>
+      <c r="A150" s="18"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -5087,7 +4274,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="21"/>
+      <c r="A151" s="18"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -5109,7 +4296,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="21"/>
+      <c r="A152" s="18"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -5131,7 +4318,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="21"/>
+      <c r="A153" s="18"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -5153,7 +4340,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="21"/>
+      <c r="A154" s="18"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -5175,7 +4362,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="21"/>
+      <c r="A155" s="18"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -5197,7 +4384,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="21"/>
+      <c r="A156" s="18"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -5219,7 +4406,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="21"/>
+      <c r="A157" s="18"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -5241,7 +4428,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="21"/>
+      <c r="A158" s="18"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -5263,7 +4450,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="21"/>
+      <c r="A159" s="18"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -5285,7 +4472,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="21"/>
+      <c r="A160" s="18"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -5307,7 +4494,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="21"/>
+      <c r="A161" s="18"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -5329,7 +4516,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="21"/>
+      <c r="A162" s="18"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -5351,7 +4538,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="21"/>
+      <c r="A163" s="18"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -5373,7 +4560,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="21"/>
+      <c r="A164" s="18"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -5395,7 +4582,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="21"/>
+      <c r="A165" s="18"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -5417,7 +4604,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="21"/>
+      <c r="A166" s="18"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5439,7 +4626,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="21"/>
+      <c r="A167" s="18"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5461,7 +4648,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="21"/>
+      <c r="A168" s="18"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5483,7 +4670,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="21"/>
+      <c r="A169" s="18"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5505,7 +4692,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="21"/>
+      <c r="A170" s="18"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5527,7 +4714,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="21"/>
+      <c r="A171" s="18"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5549,7 +4736,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="21"/>
+      <c r="A172" s="18"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -5571,7 +4758,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="21"/>
+      <c r="A173" s="18"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5593,7 +4780,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="21"/>
+      <c r="A174" s="18"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5615,7 +4802,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="21"/>
+      <c r="A175" s="18"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5637,7 +4824,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="21"/>
+      <c r="A176" s="18"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5659,7 +4846,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="21"/>
+      <c r="A177" s="18"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5681,7 +4868,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="21"/>
+      <c r="A178" s="18"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5703,7 +4890,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="21"/>
+      <c r="A179" s="18"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5725,7 +4912,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="21"/>
+      <c r="A180" s="18"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5747,7 +4934,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="21"/>
+      <c r="A181" s="18"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5769,7 +4956,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="21"/>
+      <c r="A182" s="18"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5791,7 +4978,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="21"/>
+      <c r="A183" s="18"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5813,7 +5000,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="21"/>
+      <c r="A184" s="18"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5835,7 +5022,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="21"/>
+      <c r="A185" s="18"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5857,7 +5044,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="21"/>
+      <c r="A186" s="18"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5879,7 +5066,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="21"/>
+      <c r="A187" s="18"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5901,7 +5088,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="21"/>
+      <c r="A188" s="18"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5923,7 +5110,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="21"/>
+      <c r="A189" s="18"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5945,7 +5132,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="21"/>
+      <c r="A190" s="18"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5967,7 +5154,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="21"/>
+      <c r="A191" s="18"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5989,7 +5176,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="21"/>
+      <c r="A192" s="18"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -6011,7 +5198,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="21"/>
+      <c r="A193" s="18"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -6033,7 +5220,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="21"/>
+      <c r="A194" s="18"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -6055,7 +5242,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="21"/>
+      <c r="A195" s="18"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -6077,7 +5264,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="21"/>
+      <c r="A196" s="18"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -6099,7 +5286,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="21"/>
+      <c r="A197" s="18"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -6121,7 +5308,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="21"/>
+      <c r="A198" s="18"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -6143,7 +5330,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="21"/>
+      <c r="A199" s="18"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -6165,7 +5352,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="21"/>
+      <c r="A200" s="18"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -6187,7 +5374,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="21"/>
+      <c r="A201" s="18"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -6209,7 +5396,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="21"/>
+      <c r="A202" s="18"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -6231,7 +5418,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="21"/>
+      <c r="A203" s="18"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -6253,7 +5440,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="21"/>
+      <c r="A204" s="18"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -6275,7 +5462,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="21"/>
+      <c r="A205" s="18"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -6297,7 +5484,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="21"/>
+      <c r="A206" s="18"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -6319,7 +5506,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="21"/>
+      <c r="A207" s="18"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -6341,7 +5528,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="21"/>
+      <c r="A208" s="18"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -6363,7 +5550,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="21"/>
+      <c r="A209" s="18"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -6385,7 +5572,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="21"/>
+      <c r="A210" s="18"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -6407,7 +5594,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="21"/>
+      <c r="A211" s="18"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -6429,7 +5616,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="21"/>
+      <c r="A212" s="18"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -6451,7 +5638,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="21"/>
+      <c r="A213" s="18"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -6473,7 +5660,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="21"/>
+      <c r="A214" s="18"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -6495,7 +5682,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="21"/>
+      <c r="A215" s="18"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -6517,7 +5704,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="21"/>
+      <c r="A216" s="18"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -6539,7 +5726,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="21"/>
+      <c r="A217" s="18"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -6561,7 +5748,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="21"/>
+      <c r="A218" s="18"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -6583,7 +5770,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="21"/>
+      <c r="A219" s="18"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6605,7 +5792,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="21"/>
+      <c r="A220" s="18"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6627,7 +5814,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="21"/>
+      <c r="A221" s="18"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6649,7 +5836,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="21"/>
+      <c r="A222" s="18"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -6671,7 +5858,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="21"/>
+      <c r="A223" s="18"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -6693,7 +5880,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="21"/>
+      <c r="A224" s="18"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -6715,7 +5902,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="21"/>
+      <c r="A225" s="18"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -6737,7 +5924,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="21"/>
+      <c r="A226" s="18"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6759,7 +5946,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="21"/>
+      <c r="A227" s="18"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6781,7 +5968,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="21"/>
+      <c r="A228" s="18"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -6803,7 +5990,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="21"/>
+      <c r="A229" s="18"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -6825,7 +6012,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="21"/>
+      <c r="A230" s="18"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -6847,7 +6034,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="21"/>
+      <c r="A231" s="18"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -6869,7 +6056,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="21"/>
+      <c r="A232" s="18"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -6891,7 +6078,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="21"/>
+      <c r="A233" s="18"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -6913,7 +6100,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="21"/>
+      <c r="A234" s="18"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -6935,7 +6122,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="21"/>
+      <c r="A235" s="18"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -6957,7 +6144,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="21"/>
+      <c r="A236" s="18"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -6979,7 +6166,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="21"/>
+      <c r="A237" s="18"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -7001,7 +6188,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="21"/>
+      <c r="A238" s="18"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -7023,7 +6210,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="21"/>
+      <c r="A239" s="18"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -7045,7 +6232,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="21"/>
+      <c r="A240" s="18"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -7067,7 +6254,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="21"/>
+      <c r="A241" s="18"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -7089,7 +6276,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="21"/>
+      <c r="A242" s="18"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -7111,7 +6298,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="21"/>
+      <c r="A243" s="18"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -7133,7 +6320,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="21"/>
+      <c r="A244" s="18"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -7155,7 +6342,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="21"/>
+      <c r="A245" s="18"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -7177,7 +6364,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="21"/>
+      <c r="A246" s="18"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -7199,7 +6386,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="21"/>
+      <c r="A247" s="18"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -7221,7 +6408,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="21"/>
+      <c r="A248" s="18"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -7243,7 +6430,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="21"/>
+      <c r="A249" s="18"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -7265,7 +6452,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="21"/>
+      <c r="A250" s="18"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -7287,7 +6474,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="21"/>
+      <c r="A251" s="18"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -7309,7 +6496,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="21"/>
+      <c r="A252" s="18"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -7331,7 +6518,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="21"/>
+      <c r="A253" s="18"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -7353,7 +6540,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="21"/>
+      <c r="A254" s="18"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -7375,7 +6562,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="21"/>
+      <c r="A255" s="18"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -7397,7 +6584,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="21"/>
+      <c r="A256" s="18"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -7419,7 +6606,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="21"/>
+      <c r="A257" s="18"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -7441,7 +6628,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="21"/>
+      <c r="A258" s="18"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -7463,7 +6650,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="21"/>
+      <c r="A259" s="18"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -7485,7 +6672,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="21"/>
+      <c r="A260" s="18"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -7507,7 +6694,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="21"/>
+      <c r="A261" s="18"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -7529,7 +6716,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="21"/>
+      <c r="A262" s="18"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -7551,7 +6738,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="21"/>
+      <c r="A263" s="18"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -7573,7 +6760,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="21"/>
+      <c r="A264" s="18"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -7595,7 +6782,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="21"/>
+      <c r="A265" s="18"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7617,7 +6804,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="21"/>
+      <c r="A266" s="18"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7639,7 +6826,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="21"/>
+      <c r="A267" s="18"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7661,7 +6848,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="21"/>
+      <c r="A268" s="18"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -7683,7 +6870,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="21"/>
+      <c r="A269" s="18"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -7705,7 +6892,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="21"/>
+      <c r="A270" s="18"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -7727,7 +6914,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="21"/>
+      <c r="A271" s="18"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -7749,7 +6936,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="21"/>
+      <c r="A272" s="18"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -7771,7 +6958,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="21"/>
+      <c r="A273" s="18"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -7793,7 +6980,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="21"/>
+      <c r="A274" s="18"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -7815,7 +7002,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="21"/>
+      <c r="A275" s="18"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -7837,7 +7024,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="21"/>
+      <c r="A276" s="18"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -7859,7 +7046,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="21"/>
+      <c r="A277" s="18"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -7881,7 +7068,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="21"/>
+      <c r="A278" s="18"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -7903,7 +7090,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="21"/>
+      <c r="A279" s="18"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -7925,7 +7112,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="21"/>
+      <c r="A280" s="18"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -7947,7 +7134,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="21"/>
+      <c r="A281" s="18"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -7969,7 +7156,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="21"/>
+      <c r="A282" s="18"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -7991,7 +7178,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="21"/>
+      <c r="A283" s="18"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -8013,7 +7200,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="21"/>
+      <c r="A284" s="18"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -8035,7 +7222,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="21"/>
+      <c r="A285" s="18"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -8057,7 +7244,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="21"/>
+      <c r="A286" s="18"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -8079,7 +7266,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="21"/>
+      <c r="A287" s="18"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -8101,7 +7288,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="21"/>
+      <c r="A288" s="18"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -8123,7 +7310,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="21"/>
+      <c r="A289" s="18"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -8145,7 +7332,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="21"/>
+      <c r="A290" s="18"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -8167,7 +7354,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="21"/>
+      <c r="A291" s="18"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -8189,7 +7376,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="21"/>
+      <c r="A292" s="18"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -8211,7 +7398,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="21"/>
+      <c r="A293" s="18"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -8233,7 +7420,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="21"/>
+      <c r="A294" s="18"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -8255,7 +7442,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="21"/>
+      <c r="A295" s="18"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -8277,7 +7464,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="21"/>
+      <c r="A296" s="18"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -8299,7 +7486,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="21"/>
+      <c r="A297" s="18"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -8321,7 +7508,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="21"/>
+      <c r="A298" s="18"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -8343,7 +7530,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="21"/>
+      <c r="A299" s="18"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -8365,7 +7552,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="21"/>
+      <c r="A300" s="18"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -8387,7 +7574,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="21"/>
+      <c r="A301" s="18"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -8409,7 +7596,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="21"/>
+      <c r="A302" s="18"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -8431,7 +7618,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="21"/>
+      <c r="A303" s="18"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -8453,7 +7640,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="21"/>
+      <c r="A304" s="18"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -8475,7 +7662,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="21"/>
+      <c r="A305" s="18"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -8497,7 +7684,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="21"/>
+      <c r="A306" s="18"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -8519,7 +7706,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="21"/>
+      <c r="A307" s="18"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -8541,7 +7728,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="21"/>
+      <c r="A308" s="18"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -8563,7 +7750,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="21"/>
+      <c r="A309" s="18"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -8585,7 +7772,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="21"/>
+      <c r="A310" s="18"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8607,7 +7794,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="21"/>
+      <c r="A311" s="18"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -8629,7 +7816,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="21"/>
+      <c r="A312" s="18"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -8651,7 +7838,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="21"/>
+      <c r="A313" s="18"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -8673,7 +7860,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="21"/>
+      <c r="A314" s="18"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -8695,7 +7882,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="21"/>
+      <c r="A315" s="18"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -8717,7 +7904,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="21"/>
+      <c r="A316" s="18"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -8739,7 +7926,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="21"/>
+      <c r="A317" s="18"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -8761,7 +7948,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="21"/>
+      <c r="A318" s="18"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -8783,7 +7970,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="21"/>
+      <c r="A319" s="18"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -8805,7 +7992,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="21"/>
+      <c r="A320" s="18"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -8827,7 +8014,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="21"/>
+      <c r="A321" s="18"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -8849,7 +8036,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="21"/>
+      <c r="A322" s="18"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -8871,7 +8058,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="21"/>
+      <c r="A323" s="18"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -8893,7 +8080,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="21"/>
+      <c r="A324" s="18"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -8915,7 +8102,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="21"/>
+      <c r="A325" s="18"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -8937,7 +8124,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="21"/>
+      <c r="A326" s="18"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -8959,7 +8146,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="21"/>
+      <c r="A327" s="18"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -8981,7 +8168,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="21"/>
+      <c r="A328" s="18"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -9003,7 +8190,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="21"/>
+      <c r="A329" s="18"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -9025,7 +8212,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="21"/>
+      <c r="A330" s="18"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -9047,7 +8234,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="21"/>
+      <c r="A331" s="18"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -9069,7 +8256,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="21"/>
+      <c r="A332" s="18"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -9091,7 +8278,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="21"/>
+      <c r="A333" s="18"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -9113,7 +8300,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="21"/>
+      <c r="A334" s="18"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -9135,7 +8322,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="21"/>
+      <c r="A335" s="18"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -9157,7 +8344,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="21"/>
+      <c r="A336" s="18"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -9179,7 +8366,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="21"/>
+      <c r="A337" s="18"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -9201,7 +8388,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="21"/>
+      <c r="A338" s="18"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -9223,7 +8410,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="21"/>
+      <c r="A339" s="18"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -9245,7 +8432,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="21"/>
+      <c r="A340" s="18"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -9267,7 +8454,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="21"/>
+      <c r="A341" s="18"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -9289,7 +8476,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="21"/>
+      <c r="A342" s="18"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -9311,7 +8498,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="21"/>
+      <c r="A343" s="18"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -9333,7 +8520,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="21"/>
+      <c r="A344" s="18"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -9355,7 +8542,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="21"/>
+      <c r="A345" s="18"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -9377,7 +8564,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="21"/>
+      <c r="A346" s="18"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -9399,7 +8586,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="21"/>
+      <c r="A347" s="18"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -9421,7 +8608,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="21"/>
+      <c r="A348" s="18"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -9443,7 +8630,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="21"/>
+      <c r="A349" s="18"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -9465,7 +8652,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="21"/>
+      <c r="A350" s="18"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -9487,7 +8674,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="21"/>
+      <c r="A351" s="18"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -9509,7 +8696,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="21"/>
+      <c r="A352" s="18"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -9531,7 +8718,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="21"/>
+      <c r="A353" s="18"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -9553,7 +8740,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="21"/>
+      <c r="A354" s="18"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -9575,7 +8762,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="21"/>
+      <c r="A355" s="18"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -9597,7 +8784,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="21"/>
+      <c r="A356" s="18"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -9619,7 +8806,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="21"/>
+      <c r="A357" s="18"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -9641,7 +8828,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="21"/>
+      <c r="A358" s="18"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -9663,7 +8850,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="21"/>
+      <c r="A359" s="18"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -9685,7 +8872,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="21"/>
+      <c r="A360" s="18"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -9707,7 +8894,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="21"/>
+      <c r="A361" s="18"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -9729,7 +8916,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="21"/>
+      <c r="A362" s="18"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -9751,7 +8938,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="21"/>
+      <c r="A363" s="18"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -9773,7 +8960,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="21"/>
+      <c r="A364" s="18"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -9795,7 +8982,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="21"/>
+      <c r="A365" s="18"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -9817,7 +9004,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="21"/>
+      <c r="A366" s="18"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -9839,7 +9026,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="21"/>
+      <c r="A367" s="18"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -9861,7 +9048,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="21"/>
+      <c r="A368" s="18"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -9883,7 +9070,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="21"/>
+      <c r="A369" s="18"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -9905,7 +9092,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="21"/>
+      <c r="A370" s="18"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -9927,7 +9114,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="21"/>
+      <c r="A371" s="18"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -9949,7 +9136,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="21"/>
+      <c r="A372" s="18"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -9971,7 +9158,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="21"/>
+      <c r="A373" s="18"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -9993,7 +9180,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="21"/>
+      <c r="A374" s="18"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -10015,7 +9202,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="21"/>
+      <c r="A375" s="18"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -10037,7 +9224,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="21"/>
+      <c r="A376" s="18"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -10059,7 +9246,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="21"/>
+      <c r="A377" s="18"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -10081,7 +9268,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="21"/>
+      <c r="A378" s="18"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -10103,7 +9290,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="21"/>
+      <c r="A379" s="18"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -10125,7 +9312,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="21"/>
+      <c r="A380" s="18"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -10147,7 +9334,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="21"/>
+      <c r="A381" s="18"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -10169,7 +9356,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="21"/>
+      <c r="A382" s="18"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -10191,7 +9378,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="21"/>
+      <c r="A383" s="18"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -10213,7 +9400,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="21"/>
+      <c r="A384" s="18"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -10235,7 +9422,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="21"/>
+      <c r="A385" s="18"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -10257,7 +9444,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="21"/>
+      <c r="A386" s="18"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -10279,7 +9466,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="21"/>
+      <c r="A387" s="18"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -10301,7 +9488,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="21"/>
+      <c r="A388" s="18"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -10323,7 +9510,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="21"/>
+      <c r="A389" s="18"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -10345,7 +9532,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="21"/>
+      <c r="A390" s="18"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -10367,7 +9554,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="21"/>
+      <c r="A391" s="18"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -10389,7 +9576,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="21"/>
+      <c r="A392" s="18"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -10411,7 +9598,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="21"/>
+      <c r="A393" s="18"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -10433,7 +9620,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="21"/>
+      <c r="A394" s="18"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -10455,7 +9642,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="21"/>
+      <c r="A395" s="18"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -10477,7 +9664,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="21"/>
+      <c r="A396" s="18"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -10499,7 +9686,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="21"/>
+      <c r="A397" s="18"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -10521,7 +9708,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="21"/>
+      <c r="A398" s="18"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -10543,7 +9730,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="21"/>
+      <c r="A399" s="18"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -10565,7 +9752,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="21"/>
+      <c r="A400" s="18"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -10587,7 +9774,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="21"/>
+      <c r="A401" s="18"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>
@@ -10622,28 +9809,16 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K22 K36:K401" type="list">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K401" type="list">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L22 L36:L401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L401" type="list">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M22 M36:M401" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="equal" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K23:K35" type="list">
-      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L23:L35" type="list">
-      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M23:M35" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M401" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -191,7 +191,136 @@
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Today 66 day completed at ihub.</t>
+    <t xml:space="preserve">good times </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hanging out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestest unexpected day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">another unexpected day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memorable day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">travelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">first day at the university </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well and good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hectic  DAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not that boring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">travelled back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visited temple with friends </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Came back by evening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did some coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all well ends well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekend hoorah!!!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">did some research on tools </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired even after sleeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning da vinci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roaming market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired very much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relaxed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early got up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">made some notes da vinci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hectic Monday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create project outline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very long day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good satisfied day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mechanically stuck but good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slept for recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tried from sleeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lazy Monday</t>
   </si>
 </sst>
 </file>
@@ -388,7 +517,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -458,6 +587,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1106,865 +1247,1741 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="12" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" s="15" t="n">
         <f aca="false">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J7" s="15" t="n">
         <f aca="false">IF(I7="","",1440-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="12" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" s="15" t="n">
         <f aca="false">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J8" s="15" t="n">
         <f aca="false">IF(I8="","",1440-I8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="12" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" s="15" t="n">
         <f aca="false">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J9" s="15" t="n">
         <f aca="false">IF(I9="","",1440-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="12" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>410</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I10" s="15" t="n">
         <f aca="false">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J10" s="15" t="n">
         <f aca="false">IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="12" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I11" s="15" t="n">
         <f aca="false">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J11" s="15" t="n">
         <f aca="false">IF(I11="","",1440-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="12" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15" t="n">
         <f aca="false">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J12" s="15" t="n">
         <f aca="false">IF(I12="","",1440-I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="12" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>430</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15" t="n">
         <f aca="false">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J13" s="15" t="n">
         <f aca="false">IF(I13="","",1440-I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="12" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I14" s="15" t="n">
         <f aca="false">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J14" s="15" t="n">
         <f aca="false">IF(I14="","",1440-I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="12" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>410</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="18" t="n">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J15" s="18" t="n">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="12" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I16" s="15" t="n">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J16" s="15" t="n">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="12" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15" t="n">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="12" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>360</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15" t="n">
         <f aca="false">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J18" s="15" t="n">
         <f aca="false">IF(I18="","",1440-I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="12" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15" t="n">
         <f aca="false">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <f aca="false">IF(I19="","",1440-I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="12" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="I20" s="15" t="n">
         <f aca="false">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J20" s="15" t="n">
         <f aca="false">IF(I20="","",1440-I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="12" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>410</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I21" s="15" t="n">
         <f aca="false">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J21" s="15" t="n">
         <f aca="false">IF(I21="","",1440-I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="12" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15" t="n">
         <f aca="false">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J22" s="15" t="n">
         <f aca="false">IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="12" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" s="15" t="n">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J23" s="15" t="n">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="12" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" s="15" t="n">
         <f aca="false">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J24" s="15" t="n">
         <f aca="false">IF(I24="","",1440-I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="12" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>360</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="15" t="n">
         <f aca="false">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J25" s="15" t="n">
         <f aca="false">IF(I25="","",1440-I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="12" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I26" s="15" t="n">
         <f aca="false">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J26" s="15" t="n">
         <f aca="false">IF(I26="","",1440-I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="12" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I27" s="15" t="n">
         <f aca="false">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J27" s="15" t="n">
         <f aca="false">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="12" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I28" s="15" t="n">
         <f aca="false">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J28" s="15" t="n">
         <f aca="false">IF(I28="","",1440-I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="12" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15" t="n">
         <f aca="false">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J29" s="15" t="n">
         <f aca="false">IF(I29="","",1440-I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="12" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" s="15" t="n">
         <f aca="false">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J30" s="15" t="n">
         <f aca="false">IF(I30="","",1440-I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="12" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I31" s="15" t="n">
         <f aca="false">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J31" s="15" t="n">
         <f aca="false">IF(I31="","",1440-I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="12" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>410</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" s="15" t="n">
         <f aca="false">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J32" s="15" t="n">
         <f aca="false">IF(I32="","",1440-I32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="12" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>460</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I33" s="15" t="n">
         <f aca="false">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J33" s="15" t="n">
         <f aca="false">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="12" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15" t="n">
         <f aca="false">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J34" s="15" t="n">
         <f aca="false">IF(I34="","",1440-I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="12" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I35" s="15" t="n">
         <f aca="false">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J35" s="15" t="n">
         <f aca="false">IF(I35="","",1440-I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>880</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="12" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15" t="n">
         <f aca="false">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J36" s="15" t="n">
         <f aca="false">IF(I36="","",1440-I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="12" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I37" s="15" t="n">
         <f aca="false">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J37" s="15" t="n">
         <f aca="false">IF(I37="","",1440-I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="12" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I38" s="15" t="n">
         <f aca="false">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J38" s="15" t="n">
         <f aca="false">IF(I38="","",1440-I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="12" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>370</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I39" s="15" t="n">
         <f aca="false">IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J39" s="15" t="n">
         <f aca="false">IF(I39="","",1440-I39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="12" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I40" s="15" t="n">
         <f aca="false">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J40" s="15" t="n">
         <f aca="false">IF(I40="","",1440-I40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="12" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" s="15" t="n">
         <f aca="false">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J41" s="15" t="n">
         <f aca="false">IF(I41="","",1440-I41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="12" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" s="15" t="n">
         <f aca="false">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J42" s="15" t="n">
         <f aca="false">IF(I42="","",1440-I42)</f>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="12" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I43" s="15" t="n">
         <f aca="false">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J43" s="15" t="n">
         <f aca="false">IF(I43="","",1440-I43)</f>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18"/>
+      <c r="A44" s="12"/>
       <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f aca="false">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f aca="false">IF(I44="","",1440-I44)</f>
-        <v/>
-      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18"/>
+      <c r="A45" s="12"/>
       <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f aca="false">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f aca="false">IF(I45="","",1440-I45)</f>
-        <v/>
-      </c>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
       <c r="K45" s="16"/>
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -1986,7 +3003,7 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2008,7 +3025,7 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2030,7 +3047,7 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2052,7 +3069,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2074,7 +3091,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2096,7 +3113,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2118,7 +3135,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2140,7 +3157,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -2162,7 +3179,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -2184,7 +3201,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -2206,7 +3223,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -2228,7 +3245,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -2250,7 +3267,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -2272,7 +3289,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -2294,7 +3311,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -2316,7 +3333,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -2338,7 +3355,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -2360,7 +3377,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -2382,7 +3399,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -2404,7 +3421,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="18"/>
+      <c r="A66" s="21"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -2426,7 +3443,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="18"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -2448,7 +3465,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -2470,7 +3487,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="18"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -2492,7 +3509,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="18"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -2514,7 +3531,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="18"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -2536,7 +3553,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="18"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -2558,7 +3575,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="18"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -2580,7 +3597,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="18"/>
+      <c r="A74" s="21"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -2602,7 +3619,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="18"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -2624,7 +3641,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="18"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -2646,7 +3663,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="18"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -2668,7 +3685,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="18"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -2690,7 +3707,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="18"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -2712,7 +3729,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="18"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -2734,7 +3751,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -2756,7 +3773,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="18"/>
+      <c r="A82" s="21"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -2778,7 +3795,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="18"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -2800,7 +3817,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18"/>
+      <c r="A84" s="21"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -2822,7 +3839,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="18"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -2844,7 +3861,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="18"/>
+      <c r="A86" s="21"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -2866,7 +3883,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="18"/>
+      <c r="A87" s="21"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -2888,7 +3905,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="18"/>
+      <c r="A88" s="21"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -2910,7 +3927,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="18"/>
+      <c r="A89" s="21"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -2932,7 +3949,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="18"/>
+      <c r="A90" s="21"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -2954,7 +3971,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="18"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -2976,7 +3993,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="18"/>
+      <c r="A92" s="21"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -2998,7 +4015,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="18"/>
+      <c r="A93" s="21"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3020,7 +4037,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="18"/>
+      <c r="A94" s="21"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3042,7 +4059,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="18"/>
+      <c r="A95" s="21"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3064,7 +4081,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="18"/>
+      <c r="A96" s="21"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3086,7 +4103,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="18"/>
+      <c r="A97" s="21"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3108,7 +4125,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="18"/>
+      <c r="A98" s="21"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3130,7 +4147,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="18"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3152,7 +4169,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="18"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -3174,7 +4191,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="18"/>
+      <c r="A101" s="21"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -3196,7 +4213,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="18"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -3218,7 +4235,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="18"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -3240,7 +4257,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="18"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -3262,7 +4279,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="18"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -3284,7 +4301,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="18"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -3306,7 +4323,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="18"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -3328,7 +4345,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="18"/>
+      <c r="A108" s="21"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -3350,7 +4367,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="18"/>
+      <c r="A109" s="21"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -3372,7 +4389,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="18"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -3394,7 +4411,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="18"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -3416,7 +4433,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="18"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -3438,7 +4455,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="18"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -3460,7 +4477,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="18"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -3482,7 +4499,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="18"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -3504,7 +4521,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="18"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -3526,7 +4543,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="18"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -3548,7 +4565,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="18"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -3570,7 +4587,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="18"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -3592,7 +4609,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="18"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -3614,7 +4631,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="18"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -3636,7 +4653,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="18"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -3658,7 +4675,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="18"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -3680,7 +4697,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="18"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -3702,7 +4719,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="18"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -3724,7 +4741,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="18"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -3746,7 +4763,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="18"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -3768,7 +4785,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="18"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -3790,7 +4807,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="18"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -3812,7 +4829,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="18"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -3834,7 +4851,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="18"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -3856,7 +4873,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="18"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -3878,7 +4895,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="18"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -3900,7 +4917,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="18"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -3922,7 +4939,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="18"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -3944,7 +4961,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="18"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -3966,7 +4983,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="18"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -3988,7 +5005,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="18"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4010,7 +5027,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="18"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4032,7 +5049,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="18"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4054,7 +5071,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="18"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4076,7 +5093,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="18"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4098,7 +5115,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="18"/>
+      <c r="A143" s="21"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4120,7 +5137,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="18"/>
+      <c r="A144" s="21"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4142,7 +5159,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="18"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4164,7 +5181,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="18"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4186,7 +5203,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="18"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -4208,7 +5225,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="18"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -4230,7 +5247,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="18"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -4252,7 +5269,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="18"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -4274,7 +5291,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="18"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -4296,7 +5313,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="18"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -4318,7 +5335,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="18"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -4340,7 +5357,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="18"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -4362,7 +5379,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="18"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -4384,7 +5401,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="18"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -4406,7 +5423,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="18"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -4428,7 +5445,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="18"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -4450,7 +5467,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="18"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -4472,7 +5489,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="18"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -4494,7 +5511,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="18"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -4516,7 +5533,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="18"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -4538,7 +5555,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="18"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -4560,7 +5577,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="18"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -4582,7 +5599,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="18"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -4604,7 +5621,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="18"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -4626,7 +5643,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="18"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -4648,7 +5665,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="18"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -4670,7 +5687,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="18"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -4692,7 +5709,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="18"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -4714,7 +5731,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="18"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -4736,7 +5753,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="18"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -4758,7 +5775,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="18"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -4780,7 +5797,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="18"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -4802,7 +5819,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="18"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -4824,7 +5841,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="18"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -4846,7 +5863,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="18"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -4868,7 +5885,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="18"/>
+      <c r="A178" s="21"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -4890,7 +5907,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="18"/>
+      <c r="A179" s="21"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -4912,7 +5929,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="18"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -4934,7 +5951,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="18"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -4956,7 +5973,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="18"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -4978,7 +5995,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="18"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5000,7 +6017,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="18"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5022,7 +6039,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="18"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5044,7 +6061,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="18"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5066,7 +6083,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="18"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5088,7 +6105,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="18"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5110,7 +6127,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="18"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5132,7 +6149,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="18"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5154,7 +6171,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="18"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5176,7 +6193,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="18"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -5198,7 +6215,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="18"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -5220,7 +6237,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="18"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -5242,7 +6259,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="18"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -5264,7 +6281,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="18"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -5286,7 +6303,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="18"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -5308,7 +6325,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="18"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -5330,7 +6347,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="18"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -5352,7 +6369,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="18"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -5374,7 +6391,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="18"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -5396,7 +6413,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="18"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -5418,7 +6435,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="18"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -5440,7 +6457,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="18"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -5462,7 +6479,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="18"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -5484,7 +6501,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="18"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -5506,7 +6523,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="18"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -5528,7 +6545,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="18"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -5550,7 +6567,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="18"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -5572,7 +6589,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="18"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -5594,7 +6611,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="18"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -5616,7 +6633,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="18"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -5638,7 +6655,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="18"/>
+      <c r="A213" s="21"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -5660,7 +6677,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="18"/>
+      <c r="A214" s="21"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -5682,7 +6699,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="18"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -5704,7 +6721,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="18"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -5726,7 +6743,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="18"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -5748,7 +6765,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="18"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -5770,7 +6787,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="18"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -5792,7 +6809,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="18"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -5814,7 +6831,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="18"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -5836,7 +6853,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="18"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -5858,7 +6875,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="18"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -5880,7 +6897,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="18"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -5902,7 +6919,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="18"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -5924,7 +6941,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="18"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -5946,7 +6963,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="18"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -5968,7 +6985,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="18"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -5990,7 +7007,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="18"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -6012,7 +7029,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="18"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -6034,7 +7051,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="18"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -6056,7 +7073,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="18"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -6078,7 +7095,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="18"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -6100,7 +7117,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="18"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -6122,7 +7139,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="18"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -6144,7 +7161,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="18"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -6166,7 +7183,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="18"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -6188,7 +7205,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="18"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -6210,7 +7227,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="18"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -6232,7 +7249,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="18"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -6254,7 +7271,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="18"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -6276,7 +7293,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="18"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -6298,7 +7315,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="18"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -6320,7 +7337,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="18"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -6342,7 +7359,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="18"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -6364,7 +7381,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="18"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -6386,7 +7403,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="18"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -6408,7 +7425,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="18"/>
+      <c r="A248" s="21"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -6430,7 +7447,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="18"/>
+      <c r="A249" s="21"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -6452,7 +7469,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="18"/>
+      <c r="A250" s="21"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -6474,7 +7491,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="18"/>
+      <c r="A251" s="21"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -6496,7 +7513,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="18"/>
+      <c r="A252" s="21"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -6518,7 +7535,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="18"/>
+      <c r="A253" s="21"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -6540,7 +7557,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="18"/>
+      <c r="A254" s="21"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -6562,7 +7579,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="18"/>
+      <c r="A255" s="21"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -6584,7 +7601,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="18"/>
+      <c r="A256" s="21"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -6606,7 +7623,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="18"/>
+      <c r="A257" s="21"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -6628,7 +7645,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="18"/>
+      <c r="A258" s="21"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -6650,7 +7667,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="18"/>
+      <c r="A259" s="21"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -6672,7 +7689,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="18"/>
+      <c r="A260" s="21"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -6694,7 +7711,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="18"/>
+      <c r="A261" s="21"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -6716,7 +7733,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="18"/>
+      <c r="A262" s="21"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -6738,7 +7755,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="18"/>
+      <c r="A263" s="21"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -6760,7 +7777,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="18"/>
+      <c r="A264" s="21"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -6782,7 +7799,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="18"/>
+      <c r="A265" s="21"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -6804,7 +7821,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="18"/>
+      <c r="A266" s="21"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -6826,7 +7843,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="18"/>
+      <c r="A267" s="21"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -6848,7 +7865,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="18"/>
+      <c r="A268" s="21"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -6870,7 +7887,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="18"/>
+      <c r="A269" s="21"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -6892,7 +7909,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="18"/>
+      <c r="A270" s="21"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -6914,7 +7931,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="18"/>
+      <c r="A271" s="21"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -6936,7 +7953,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="18"/>
+      <c r="A272" s="21"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -6958,7 +7975,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="18"/>
+      <c r="A273" s="21"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -6980,7 +7997,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="18"/>
+      <c r="A274" s="21"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -7002,7 +8019,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="18"/>
+      <c r="A275" s="21"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -7024,7 +8041,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="18"/>
+      <c r="A276" s="21"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -7046,7 +8063,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="18"/>
+      <c r="A277" s="21"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -7068,7 +8085,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="18"/>
+      <c r="A278" s="21"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -7090,7 +8107,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="18"/>
+      <c r="A279" s="21"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -7112,7 +8129,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="18"/>
+      <c r="A280" s="21"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -7134,7 +8151,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="18"/>
+      <c r="A281" s="21"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -7156,7 +8173,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="18"/>
+      <c r="A282" s="21"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -7178,7 +8195,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="18"/>
+      <c r="A283" s="21"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -7200,7 +8217,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="18"/>
+      <c r="A284" s="21"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -7222,7 +8239,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="18"/>
+      <c r="A285" s="21"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -7244,7 +8261,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="18"/>
+      <c r="A286" s="21"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -7266,7 +8283,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="18"/>
+      <c r="A287" s="21"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -7288,7 +8305,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="18"/>
+      <c r="A288" s="21"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -7310,7 +8327,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="18"/>
+      <c r="A289" s="21"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -7332,7 +8349,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="18"/>
+      <c r="A290" s="21"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -7354,7 +8371,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="18"/>
+      <c r="A291" s="21"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -7376,7 +8393,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="18"/>
+      <c r="A292" s="21"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -7398,7 +8415,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="18"/>
+      <c r="A293" s="21"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -7420,7 +8437,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="18"/>
+      <c r="A294" s="21"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -7442,7 +8459,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="18"/>
+      <c r="A295" s="21"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -7464,7 +8481,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="18"/>
+      <c r="A296" s="21"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -7486,7 +8503,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="18"/>
+      <c r="A297" s="21"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -7508,7 +8525,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="18"/>
+      <c r="A298" s="21"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -7530,7 +8547,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="18"/>
+      <c r="A299" s="21"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -7552,7 +8569,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="18"/>
+      <c r="A300" s="21"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -7574,7 +8591,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="18"/>
+      <c r="A301" s="21"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -7596,7 +8613,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="18"/>
+      <c r="A302" s="21"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -7618,7 +8635,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="18"/>
+      <c r="A303" s="21"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -7640,7 +8657,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="18"/>
+      <c r="A304" s="21"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -7662,7 +8679,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="18"/>
+      <c r="A305" s="21"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -7684,7 +8701,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="18"/>
+      <c r="A306" s="21"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -7706,7 +8723,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="18"/>
+      <c r="A307" s="21"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -7728,7 +8745,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="18"/>
+      <c r="A308" s="21"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -7750,7 +8767,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="18"/>
+      <c r="A309" s="21"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -7772,7 +8789,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="18"/>
+      <c r="A310" s="21"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -7794,7 +8811,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="18"/>
+      <c r="A311" s="21"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -7816,7 +8833,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="18"/>
+      <c r="A312" s="21"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -7838,7 +8855,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="18"/>
+      <c r="A313" s="21"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -7860,7 +8877,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="18"/>
+      <c r="A314" s="21"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -7882,7 +8899,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="18"/>
+      <c r="A315" s="21"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -7904,7 +8921,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="18"/>
+      <c r="A316" s="21"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -7926,7 +8943,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="18"/>
+      <c r="A317" s="21"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -7948,7 +8965,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="18"/>
+      <c r="A318" s="21"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -7970,7 +8987,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="18"/>
+      <c r="A319" s="21"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -7992,7 +9009,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="18"/>
+      <c r="A320" s="21"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -8014,7 +9031,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="18"/>
+      <c r="A321" s="21"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -8036,7 +9053,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="18"/>
+      <c r="A322" s="21"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -8058,7 +9075,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="18"/>
+      <c r="A323" s="21"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -8080,7 +9097,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="18"/>
+      <c r="A324" s="21"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -8102,7 +9119,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="18"/>
+      <c r="A325" s="21"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -8124,7 +9141,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="18"/>
+      <c r="A326" s="21"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -8146,7 +9163,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="18"/>
+      <c r="A327" s="21"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -8168,7 +9185,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="18"/>
+      <c r="A328" s="21"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -8190,7 +9207,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="18"/>
+      <c r="A329" s="21"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -8212,7 +9229,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="18"/>
+      <c r="A330" s="21"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -8234,7 +9251,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="18"/>
+      <c r="A331" s="21"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -8256,7 +9273,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="18"/>
+      <c r="A332" s="21"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -8278,7 +9295,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="18"/>
+      <c r="A333" s="21"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -8300,7 +9317,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="18"/>
+      <c r="A334" s="21"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -8322,7 +9339,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="18"/>
+      <c r="A335" s="21"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -8344,7 +9361,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="18"/>
+      <c r="A336" s="21"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -8366,7 +9383,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="18"/>
+      <c r="A337" s="21"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -8388,7 +9405,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="18"/>
+      <c r="A338" s="21"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -8410,7 +9427,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="18"/>
+      <c r="A339" s="21"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -8432,7 +9449,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="18"/>
+      <c r="A340" s="21"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -8454,7 +9471,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="18"/>
+      <c r="A341" s="21"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -8476,7 +9493,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="18"/>
+      <c r="A342" s="21"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -8498,7 +9515,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="18"/>
+      <c r="A343" s="21"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -8520,7 +9537,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="18"/>
+      <c r="A344" s="21"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -8542,7 +9559,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="18"/>
+      <c r="A345" s="21"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -8564,7 +9581,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="18"/>
+      <c r="A346" s="21"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -8586,7 +9603,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="18"/>
+      <c r="A347" s="21"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -8608,7 +9625,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="18"/>
+      <c r="A348" s="21"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -8630,7 +9647,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="18"/>
+      <c r="A349" s="21"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -8652,7 +9669,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="18"/>
+      <c r="A350" s="21"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -8674,7 +9691,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="18"/>
+      <c r="A351" s="21"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -8696,7 +9713,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="18"/>
+      <c r="A352" s="21"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -8718,7 +9735,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="18"/>
+      <c r="A353" s="21"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -8740,7 +9757,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="18"/>
+      <c r="A354" s="21"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -8762,7 +9779,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="18"/>
+      <c r="A355" s="21"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -8784,7 +9801,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="18"/>
+      <c r="A356" s="21"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -8806,7 +9823,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="18"/>
+      <c r="A357" s="21"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -8828,7 +9845,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="18"/>
+      <c r="A358" s="21"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -8850,7 +9867,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="18"/>
+      <c r="A359" s="21"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -8872,7 +9889,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="18"/>
+      <c r="A360" s="21"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -8894,7 +9911,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="18"/>
+      <c r="A361" s="21"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -8916,7 +9933,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="18"/>
+      <c r="A362" s="21"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -8938,7 +9955,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="18"/>
+      <c r="A363" s="21"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -8960,7 +9977,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="18"/>
+      <c r="A364" s="21"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -8982,7 +9999,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="18"/>
+      <c r="A365" s="21"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -9004,7 +10021,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="18"/>
+      <c r="A366" s="21"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -9026,7 +10043,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="18"/>
+      <c r="A367" s="21"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -9048,7 +10065,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="18"/>
+      <c r="A368" s="21"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -9070,7 +10087,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="18"/>
+      <c r="A369" s="21"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -9092,7 +10109,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="18"/>
+      <c r="A370" s="21"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -9114,7 +10131,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="18"/>
+      <c r="A371" s="21"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -9136,7 +10153,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="18"/>
+      <c r="A372" s="21"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -9158,7 +10175,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="18"/>
+      <c r="A373" s="21"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -9180,7 +10197,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="18"/>
+      <c r="A374" s="21"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -9202,7 +10219,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="18"/>
+      <c r="A375" s="21"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -9224,7 +10241,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="18"/>
+      <c r="A376" s="21"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -9246,7 +10263,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="18"/>
+      <c r="A377" s="21"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -9268,7 +10285,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="18"/>
+      <c r="A378" s="21"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -9290,7 +10307,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="18"/>
+      <c r="A379" s="21"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -9312,7 +10329,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="18"/>
+      <c r="A380" s="21"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -9334,7 +10351,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="18"/>
+      <c r="A381" s="21"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -9356,7 +10373,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="18"/>
+      <c r="A382" s="21"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -9378,7 +10395,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="18"/>
+      <c r="A383" s="21"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -9400,7 +10417,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="18"/>
+      <c r="A384" s="21"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -9422,7 +10439,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="18"/>
+      <c r="A385" s="21"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -9444,7 +10461,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="18"/>
+      <c r="A386" s="21"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -9466,7 +10483,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="18"/>
+      <c r="A387" s="21"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -9488,7 +10505,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="18"/>
+      <c r="A388" s="21"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -9510,7 +10527,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="18"/>
+      <c r="A389" s="21"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -9532,7 +10549,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="18"/>
+      <c r="A390" s="21"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -9554,7 +10571,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="18"/>
+      <c r="A391" s="21"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -9576,7 +10593,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="18"/>
+      <c r="A392" s="21"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -9598,7 +10615,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="18"/>
+      <c r="A393" s="21"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -9620,7 +10637,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="18"/>
+      <c r="A394" s="21"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -9642,7 +10659,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="18"/>
+      <c r="A395" s="21"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -9664,7 +10681,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="18"/>
+      <c r="A396" s="21"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -9686,7 +10703,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="18"/>
+      <c r="A397" s="21"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -9708,7 +10725,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="18"/>
+      <c r="A398" s="21"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -9730,7 +10747,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="18"/>
+      <c r="A399" s="21"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -9752,7 +10769,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="18"/>
+      <c r="A400" s="21"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -9774,7 +10791,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="18"/>
+      <c r="A401" s="21"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>
@@ -9809,16 +10826,28 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K401" type="list">
+  <dataValidations count="6">
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K30 K46:K401" type="list">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L30 L46:L401" type="list">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M30 M46:M401" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="equal" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K31:K45" type="list">
+      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L31:L45" type="list">
+      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M31:M45" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -322,6 +322,15 @@
   <si>
     <t xml:space="preserve">lazy Monday</t>
   </si>
+  <si>
+    <t xml:space="preserve">tried solving error in project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very very much tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good day</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +341,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +456,12 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -517,7 +532,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -599,6 +614,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1990,7 +2009,7 @@
         <v>390</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>70</v>
@@ -2009,11 +2028,11 @@
       </c>
       <c r="I23" s="15" t="n">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v>880</v>
+        <v>850</v>
       </c>
       <c r="J23" s="15" t="n">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>58</v>
@@ -2910,7 +2929,7 @@
         <v>300</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D43" s="13" t="n">
         <v>50</v>
@@ -2918,22 +2937,22 @@
       <c r="E43" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F43" s="14" t="n">
+      <c r="F43" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="G43" s="13" t="n">
         <v>6</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I43" s="15" t="n">
         <f aca="false">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="J43" s="15" t="n">
         <f aca="false">IF(I43="","",1440-I43)</f>
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>57</v>
@@ -2949,83 +2968,191 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+      <c r="A44" s="12" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <f aca="false">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <v>830</v>
+      </c>
+      <c r="J44" s="15" t="n">
+        <f aca="false">IF(I44="","",1440-I44)</f>
+        <v>610</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="A45" s="12" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <f aca="false">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <v>1060</v>
+      </c>
+      <c r="J45" s="15" t="n">
+        <f aca="false">IF(I45="","",1440-I45)</f>
+        <v>380</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="12" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I46" s="15" t="n">
         <f aca="false">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J46" s="15" t="n">
         <f aca="false">IF(I46="","",1440-I46)</f>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="21" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="12" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I47" s="15" t="n">
         <f aca="false">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J47" s="15" t="n">
         <f aca="false">IF(I47="","",1440-I47)</f>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -3047,7 +3174,7 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -3069,7 +3196,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -3091,7 +3218,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -3113,7 +3240,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -3135,7 +3262,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -3157,7 +3284,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -3179,7 +3306,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -3201,7 +3328,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3223,7 +3350,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -3245,7 +3372,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -3267,7 +3394,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -3289,7 +3416,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3311,7 +3438,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="21"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3333,7 +3460,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3355,7 +3482,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3377,7 +3504,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21"/>
+      <c r="A64" s="22"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3399,7 +3526,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3421,7 +3548,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3443,7 +3570,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3465,7 +3592,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3487,7 +3614,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3509,7 +3636,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="21"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3531,7 +3658,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="21"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3553,7 +3680,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3575,7 +3702,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3597,7 +3724,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21"/>
+      <c r="A74" s="22"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3619,7 +3746,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="21"/>
+      <c r="A75" s="22"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3641,7 +3768,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="21"/>
+      <c r="A76" s="22"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3663,7 +3790,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="21"/>
+      <c r="A77" s="22"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3685,7 +3812,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="21"/>
+      <c r="A78" s="22"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3707,7 +3834,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="21"/>
+      <c r="A79" s="22"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3729,7 +3856,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="21"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3751,7 +3878,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3773,7 +3900,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21"/>
+      <c r="A82" s="22"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3795,7 +3922,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3817,7 +3944,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="21"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3839,7 +3966,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="21"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3861,7 +3988,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21"/>
+      <c r="A86" s="22"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3883,7 +4010,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3905,7 +4032,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="21"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3927,7 +4054,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="21"/>
+      <c r="A89" s="22"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3949,7 +4076,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="21"/>
+      <c r="A90" s="22"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3971,7 +4098,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="21"/>
+      <c r="A91" s="22"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3993,7 +4120,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="21"/>
+      <c r="A92" s="22"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -4015,7 +4142,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="21"/>
+      <c r="A93" s="22"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -4037,7 +4164,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="21"/>
+      <c r="A94" s="22"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -4059,7 +4186,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="21"/>
+      <c r="A95" s="22"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -4081,7 +4208,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="21"/>
+      <c r="A96" s="22"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -4103,7 +4230,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="21"/>
+      <c r="A97" s="22"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -4125,7 +4252,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="21"/>
+      <c r="A98" s="22"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -4147,7 +4274,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="21"/>
+      <c r="A99" s="22"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -4169,7 +4296,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="21"/>
+      <c r="A100" s="22"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -4191,7 +4318,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="21"/>
+      <c r="A101" s="22"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -4213,7 +4340,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="21"/>
+      <c r="A102" s="22"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -4235,7 +4362,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="21"/>
+      <c r="A103" s="22"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -4257,7 +4384,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="21"/>
+      <c r="A104" s="22"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -4279,7 +4406,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="21"/>
+      <c r="A105" s="22"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -4301,7 +4428,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="21"/>
+      <c r="A106" s="22"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -4323,7 +4450,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="21"/>
+      <c r="A107" s="22"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -4345,7 +4472,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="21"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -4367,7 +4494,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="21"/>
+      <c r="A109" s="22"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -4389,7 +4516,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="21"/>
+      <c r="A110" s="22"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -4411,7 +4538,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="21"/>
+      <c r="A111" s="22"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -4433,7 +4560,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="21"/>
+      <c r="A112" s="22"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -4455,7 +4582,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="21"/>
+      <c r="A113" s="22"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -4477,7 +4604,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="21"/>
+      <c r="A114" s="22"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -4499,7 +4626,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="21"/>
+      <c r="A115" s="22"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4521,7 +4648,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="21"/>
+      <c r="A116" s="22"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4543,7 +4670,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="21"/>
+      <c r="A117" s="22"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4565,7 +4692,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="21"/>
+      <c r="A118" s="22"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4587,7 +4714,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="21"/>
+      <c r="A119" s="22"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -4609,7 +4736,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="21"/>
+      <c r="A120" s="22"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -4631,7 +4758,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="21"/>
+      <c r="A121" s="22"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -4653,7 +4780,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="21"/>
+      <c r="A122" s="22"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -4675,7 +4802,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="21"/>
+      <c r="A123" s="22"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -4697,7 +4824,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="21"/>
+      <c r="A124" s="22"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -4719,7 +4846,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="21"/>
+      <c r="A125" s="22"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -4741,7 +4868,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="21"/>
+      <c r="A126" s="22"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4763,7 +4890,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="21"/>
+      <c r="A127" s="22"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4785,7 +4912,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="21"/>
+      <c r="A128" s="22"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4807,7 +4934,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="21"/>
+      <c r="A129" s="22"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4829,7 +4956,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="21"/>
+      <c r="A130" s="22"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4851,7 +4978,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="21"/>
+      <c r="A131" s="22"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4873,7 +5000,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="21"/>
+      <c r="A132" s="22"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4895,7 +5022,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="21"/>
+      <c r="A133" s="22"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4917,7 +5044,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="21"/>
+      <c r="A134" s="22"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -4939,7 +5066,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="21"/>
+      <c r="A135" s="22"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -4961,7 +5088,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="21"/>
+      <c r="A136" s="22"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -4983,7 +5110,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="21"/>
+      <c r="A137" s="22"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -5005,7 +5132,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="21"/>
+      <c r="A138" s="22"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -5027,7 +5154,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="21"/>
+      <c r="A139" s="22"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -5049,7 +5176,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="21"/>
+      <c r="A140" s="22"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -5071,7 +5198,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="21"/>
+      <c r="A141" s="22"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -5093,7 +5220,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="21"/>
+      <c r="A142" s="22"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -5115,7 +5242,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="21"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -5137,7 +5264,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="21"/>
+      <c r="A144" s="22"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -5159,7 +5286,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="21"/>
+      <c r="A145" s="22"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -5181,7 +5308,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="21"/>
+      <c r="A146" s="22"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -5203,7 +5330,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="21"/>
+      <c r="A147" s="22"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -5225,7 +5352,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="21"/>
+      <c r="A148" s="22"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -5247,7 +5374,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="21"/>
+      <c r="A149" s="22"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -5269,7 +5396,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="21"/>
+      <c r="A150" s="22"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -5291,7 +5418,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="21"/>
+      <c r="A151" s="22"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -5313,7 +5440,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="21"/>
+      <c r="A152" s="22"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -5335,7 +5462,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="21"/>
+      <c r="A153" s="22"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -5357,7 +5484,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="21"/>
+      <c r="A154" s="22"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -5379,7 +5506,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="21"/>
+      <c r="A155" s="22"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -5401,7 +5528,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="21"/>
+      <c r="A156" s="22"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -5423,7 +5550,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="21"/>
+      <c r="A157" s="22"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -5445,7 +5572,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="21"/>
+      <c r="A158" s="22"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -5467,7 +5594,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="21"/>
+      <c r="A159" s="22"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -5489,7 +5616,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="21"/>
+      <c r="A160" s="22"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -5511,7 +5638,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="21"/>
+      <c r="A161" s="22"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -5533,7 +5660,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="21"/>
+      <c r="A162" s="22"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -5555,7 +5682,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="21"/>
+      <c r="A163" s="22"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -5577,7 +5704,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="21"/>
+      <c r="A164" s="22"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -5599,7 +5726,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="21"/>
+      <c r="A165" s="22"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -5621,7 +5748,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="21"/>
+      <c r="A166" s="22"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5643,7 +5770,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="21"/>
+      <c r="A167" s="22"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5665,7 +5792,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="21"/>
+      <c r="A168" s="22"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5687,7 +5814,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="21"/>
+      <c r="A169" s="22"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5709,7 +5836,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="21"/>
+      <c r="A170" s="22"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5731,7 +5858,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="21"/>
+      <c r="A171" s="22"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5753,7 +5880,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="21"/>
+      <c r="A172" s="22"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -5775,7 +5902,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="21"/>
+      <c r="A173" s="22"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5797,7 +5924,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="21"/>
+      <c r="A174" s="22"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5819,7 +5946,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="21"/>
+      <c r="A175" s="22"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5841,7 +5968,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="21"/>
+      <c r="A176" s="22"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5863,7 +5990,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="21"/>
+      <c r="A177" s="22"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5885,7 +6012,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="21"/>
+      <c r="A178" s="22"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5907,7 +6034,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="21"/>
+      <c r="A179" s="22"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5929,7 +6056,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="21"/>
+      <c r="A180" s="22"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5951,7 +6078,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="21"/>
+      <c r="A181" s="22"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5973,7 +6100,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="21"/>
+      <c r="A182" s="22"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5995,7 +6122,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="21"/>
+      <c r="A183" s="22"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -6017,7 +6144,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="21"/>
+      <c r="A184" s="22"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -6039,7 +6166,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="21"/>
+      <c r="A185" s="22"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -6061,7 +6188,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="21"/>
+      <c r="A186" s="22"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -6083,7 +6210,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="21"/>
+      <c r="A187" s="22"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -6105,7 +6232,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="21"/>
+      <c r="A188" s="22"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -6127,7 +6254,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="21"/>
+      <c r="A189" s="22"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -6149,7 +6276,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="21"/>
+      <c r="A190" s="22"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -6171,7 +6298,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="21"/>
+      <c r="A191" s="22"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -6193,7 +6320,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="21"/>
+      <c r="A192" s="22"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -6215,7 +6342,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="21"/>
+      <c r="A193" s="22"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -6237,7 +6364,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="21"/>
+      <c r="A194" s="22"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -6259,7 +6386,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="21"/>
+      <c r="A195" s="22"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -6281,7 +6408,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="21"/>
+      <c r="A196" s="22"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -6303,7 +6430,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="21"/>
+      <c r="A197" s="22"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -6325,7 +6452,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="21"/>
+      <c r="A198" s="22"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -6347,7 +6474,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="21"/>
+      <c r="A199" s="22"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -6369,7 +6496,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="21"/>
+      <c r="A200" s="22"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -6391,7 +6518,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="21"/>
+      <c r="A201" s="22"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -6413,7 +6540,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="21"/>
+      <c r="A202" s="22"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -6435,7 +6562,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="21"/>
+      <c r="A203" s="22"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -6457,7 +6584,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="21"/>
+      <c r="A204" s="22"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -6479,7 +6606,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="21"/>
+      <c r="A205" s="22"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -6501,7 +6628,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="21"/>
+      <c r="A206" s="22"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -6523,7 +6650,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="21"/>
+      <c r="A207" s="22"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -6545,7 +6672,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="21"/>
+      <c r="A208" s="22"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -6567,7 +6694,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="21"/>
+      <c r="A209" s="22"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -6589,7 +6716,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="21"/>
+      <c r="A210" s="22"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -6611,7 +6738,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="21"/>
+      <c r="A211" s="22"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -6633,7 +6760,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="21"/>
+      <c r="A212" s="22"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -6655,7 +6782,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="21"/>
+      <c r="A213" s="22"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -6677,7 +6804,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="21"/>
+      <c r="A214" s="22"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -6699,7 +6826,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="21"/>
+      <c r="A215" s="22"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -6721,7 +6848,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="21"/>
+      <c r="A216" s="22"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -6743,7 +6870,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="21"/>
+      <c r="A217" s="22"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -6765,7 +6892,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="21"/>
+      <c r="A218" s="22"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -6787,7 +6914,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="21"/>
+      <c r="A219" s="22"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6809,7 +6936,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="21"/>
+      <c r="A220" s="22"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6831,7 +6958,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="21"/>
+      <c r="A221" s="22"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6853,7 +6980,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="21"/>
+      <c r="A222" s="22"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -6875,7 +7002,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="21"/>
+      <c r="A223" s="22"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -6897,7 +7024,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="21"/>
+      <c r="A224" s="22"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -6919,7 +7046,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="21"/>
+      <c r="A225" s="22"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -6941,7 +7068,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="21"/>
+      <c r="A226" s="22"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6963,7 +7090,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="21"/>
+      <c r="A227" s="22"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6985,7 +7112,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="21"/>
+      <c r="A228" s="22"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -7007,7 +7134,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="21"/>
+      <c r="A229" s="22"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -7029,7 +7156,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="21"/>
+      <c r="A230" s="22"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -7051,7 +7178,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="21"/>
+      <c r="A231" s="22"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -7073,7 +7200,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="21"/>
+      <c r="A232" s="22"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -7095,7 +7222,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="21"/>
+      <c r="A233" s="22"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -7117,7 +7244,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="21"/>
+      <c r="A234" s="22"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -7139,7 +7266,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="21"/>
+      <c r="A235" s="22"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -7161,7 +7288,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="21"/>
+      <c r="A236" s="22"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -7183,7 +7310,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="21"/>
+      <c r="A237" s="22"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -7205,7 +7332,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="21"/>
+      <c r="A238" s="22"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -7227,7 +7354,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="21"/>
+      <c r="A239" s="22"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -7249,7 +7376,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="21"/>
+      <c r="A240" s="22"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -7271,7 +7398,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="21"/>
+      <c r="A241" s="22"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -7293,7 +7420,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="21"/>
+      <c r="A242" s="22"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -7315,7 +7442,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="21"/>
+      <c r="A243" s="22"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -7337,7 +7464,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="21"/>
+      <c r="A244" s="22"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -7359,7 +7486,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="21"/>
+      <c r="A245" s="22"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -7381,7 +7508,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="21"/>
+      <c r="A246" s="22"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -7403,7 +7530,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="21"/>
+      <c r="A247" s="22"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -7425,7 +7552,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="21"/>
+      <c r="A248" s="22"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -7447,7 +7574,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="21"/>
+      <c r="A249" s="22"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -7469,7 +7596,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="21"/>
+      <c r="A250" s="22"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -7491,7 +7618,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="21"/>
+      <c r="A251" s="22"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -7513,7 +7640,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="21"/>
+      <c r="A252" s="22"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -7535,7 +7662,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="21"/>
+      <c r="A253" s="22"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -7557,7 +7684,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="21"/>
+      <c r="A254" s="22"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -7579,7 +7706,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="21"/>
+      <c r="A255" s="22"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -7601,7 +7728,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="21"/>
+      <c r="A256" s="22"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -7623,7 +7750,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="21"/>
+      <c r="A257" s="22"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -7645,7 +7772,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="21"/>
+      <c r="A258" s="22"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -7667,7 +7794,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="21"/>
+      <c r="A259" s="22"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -7689,7 +7816,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="21"/>
+      <c r="A260" s="22"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -7711,7 +7838,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="21"/>
+      <c r="A261" s="22"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -7733,7 +7860,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="21"/>
+      <c r="A262" s="22"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -7755,7 +7882,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="21"/>
+      <c r="A263" s="22"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -7777,7 +7904,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="21"/>
+      <c r="A264" s="22"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -7799,7 +7926,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="21"/>
+      <c r="A265" s="22"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7821,7 +7948,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="21"/>
+      <c r="A266" s="22"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7843,7 +7970,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="21"/>
+      <c r="A267" s="22"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7865,7 +7992,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="21"/>
+      <c r="A268" s="22"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -7887,7 +8014,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="21"/>
+      <c r="A269" s="22"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -7909,7 +8036,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="21"/>
+      <c r="A270" s="22"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -7931,7 +8058,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="21"/>
+      <c r="A271" s="22"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -7953,7 +8080,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="21"/>
+      <c r="A272" s="22"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -7975,7 +8102,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="21"/>
+      <c r="A273" s="22"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -7997,7 +8124,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="21"/>
+      <c r="A274" s="22"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -8019,7 +8146,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="21"/>
+      <c r="A275" s="22"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -8041,7 +8168,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="21"/>
+      <c r="A276" s="22"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -8063,7 +8190,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="21"/>
+      <c r="A277" s="22"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -8085,7 +8212,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="21"/>
+      <c r="A278" s="22"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -8107,7 +8234,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="21"/>
+      <c r="A279" s="22"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -8129,7 +8256,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="21"/>
+      <c r="A280" s="22"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -8151,7 +8278,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="21"/>
+      <c r="A281" s="22"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -8173,7 +8300,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="21"/>
+      <c r="A282" s="22"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -8195,7 +8322,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="21"/>
+      <c r="A283" s="22"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -8217,7 +8344,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="21"/>
+      <c r="A284" s="22"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -8239,7 +8366,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="21"/>
+      <c r="A285" s="22"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -8261,7 +8388,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="21"/>
+      <c r="A286" s="22"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -8283,7 +8410,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="21"/>
+      <c r="A287" s="22"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -8305,7 +8432,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="21"/>
+      <c r="A288" s="22"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -8327,7 +8454,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="21"/>
+      <c r="A289" s="22"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -8349,7 +8476,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="21"/>
+      <c r="A290" s="22"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -8371,7 +8498,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="21"/>
+      <c r="A291" s="22"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -8393,7 +8520,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="21"/>
+      <c r="A292" s="22"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -8415,7 +8542,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="21"/>
+      <c r="A293" s="22"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -8437,7 +8564,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="21"/>
+      <c r="A294" s="22"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -8459,7 +8586,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="21"/>
+      <c r="A295" s="22"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -8481,7 +8608,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="21"/>
+      <c r="A296" s="22"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -8503,7 +8630,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="21"/>
+      <c r="A297" s="22"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -8525,7 +8652,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="21"/>
+      <c r="A298" s="22"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -8547,7 +8674,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="21"/>
+      <c r="A299" s="22"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -8569,7 +8696,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="21"/>
+      <c r="A300" s="22"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -8591,7 +8718,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="21"/>
+      <c r="A301" s="22"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -8613,7 +8740,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="21"/>
+      <c r="A302" s="22"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -8635,7 +8762,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="21"/>
+      <c r="A303" s="22"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -8657,7 +8784,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="21"/>
+      <c r="A304" s="22"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -8679,7 +8806,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="21"/>
+      <c r="A305" s="22"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -8701,7 +8828,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="21"/>
+      <c r="A306" s="22"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -8723,7 +8850,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="21"/>
+      <c r="A307" s="22"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -8745,7 +8872,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="21"/>
+      <c r="A308" s="22"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -8767,7 +8894,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="21"/>
+      <c r="A309" s="22"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -8789,7 +8916,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="21"/>
+      <c r="A310" s="22"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8811,7 +8938,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="21"/>
+      <c r="A311" s="22"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -8833,7 +8960,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="21"/>
+      <c r="A312" s="22"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -8855,7 +8982,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="21"/>
+      <c r="A313" s="22"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -8877,7 +9004,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="21"/>
+      <c r="A314" s="22"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -8899,7 +9026,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="21"/>
+      <c r="A315" s="22"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -8921,7 +9048,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="21"/>
+      <c r="A316" s="22"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -8943,7 +9070,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="21"/>
+      <c r="A317" s="22"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -8965,7 +9092,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="21"/>
+      <c r="A318" s="22"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -8987,7 +9114,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="21"/>
+      <c r="A319" s="22"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -9009,7 +9136,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="21"/>
+      <c r="A320" s="22"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -9031,7 +9158,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="21"/>
+      <c r="A321" s="22"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -9053,7 +9180,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="21"/>
+      <c r="A322" s="22"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -9075,7 +9202,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="21"/>
+      <c r="A323" s="22"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -9097,7 +9224,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="21"/>
+      <c r="A324" s="22"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -9119,7 +9246,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="21"/>
+      <c r="A325" s="22"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -9141,7 +9268,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="21"/>
+      <c r="A326" s="22"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -9163,7 +9290,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="21"/>
+      <c r="A327" s="22"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -9185,7 +9312,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="21"/>
+      <c r="A328" s="22"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -9207,7 +9334,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="21"/>
+      <c r="A329" s="22"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -9229,7 +9356,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="21"/>
+      <c r="A330" s="22"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -9251,7 +9378,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="21"/>
+      <c r="A331" s="22"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -9273,7 +9400,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="21"/>
+      <c r="A332" s="22"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -9295,7 +9422,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="21"/>
+      <c r="A333" s="22"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -9317,7 +9444,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="21"/>
+      <c r="A334" s="22"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -9339,7 +9466,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="21"/>
+      <c r="A335" s="22"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -9361,7 +9488,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="21"/>
+      <c r="A336" s="22"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -9383,7 +9510,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="21"/>
+      <c r="A337" s="22"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -9405,7 +9532,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="21"/>
+      <c r="A338" s="22"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -9427,7 +9554,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="21"/>
+      <c r="A339" s="22"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -9449,7 +9576,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="21"/>
+      <c r="A340" s="22"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -9471,7 +9598,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="21"/>
+      <c r="A341" s="22"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -9493,7 +9620,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="21"/>
+      <c r="A342" s="22"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -9515,7 +9642,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="21"/>
+      <c r="A343" s="22"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -9537,7 +9664,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="21"/>
+      <c r="A344" s="22"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -9559,7 +9686,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="21"/>
+      <c r="A345" s="22"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -9581,7 +9708,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="21"/>
+      <c r="A346" s="22"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -9603,7 +9730,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="21"/>
+      <c r="A347" s="22"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -9625,7 +9752,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="21"/>
+      <c r="A348" s="22"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -9647,7 +9774,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="21"/>
+      <c r="A349" s="22"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -9669,7 +9796,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="21"/>
+      <c r="A350" s="22"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -9691,7 +9818,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="21"/>
+      <c r="A351" s="22"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -9713,7 +9840,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="21"/>
+      <c r="A352" s="22"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -9735,7 +9862,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="21"/>
+      <c r="A353" s="22"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -9757,7 +9884,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="21"/>
+      <c r="A354" s="22"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -9779,7 +9906,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="21"/>
+      <c r="A355" s="22"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -9801,7 +9928,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="21"/>
+      <c r="A356" s="22"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -9823,7 +9950,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="21"/>
+      <c r="A357" s="22"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -9845,7 +9972,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="21"/>
+      <c r="A358" s="22"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -9867,7 +9994,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="21"/>
+      <c r="A359" s="22"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -9889,7 +10016,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="21"/>
+      <c r="A360" s="22"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -9911,7 +10038,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="21"/>
+      <c r="A361" s="22"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -9933,7 +10060,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="21"/>
+      <c r="A362" s="22"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -9955,7 +10082,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="21"/>
+      <c r="A363" s="22"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -9977,7 +10104,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="21"/>
+      <c r="A364" s="22"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -9999,7 +10126,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="21"/>
+      <c r="A365" s="22"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -10021,7 +10148,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="21"/>
+      <c r="A366" s="22"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -10043,7 +10170,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="21"/>
+      <c r="A367" s="22"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -10065,7 +10192,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="21"/>
+      <c r="A368" s="22"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -10087,7 +10214,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="21"/>
+      <c r="A369" s="22"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -10109,7 +10236,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="21"/>
+      <c r="A370" s="22"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -10131,7 +10258,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="21"/>
+      <c r="A371" s="22"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -10153,7 +10280,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="21"/>
+      <c r="A372" s="22"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -10175,7 +10302,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="21"/>
+      <c r="A373" s="22"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -10197,7 +10324,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="21"/>
+      <c r="A374" s="22"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -10219,7 +10346,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="21"/>
+      <c r="A375" s="22"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -10241,7 +10368,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="21"/>
+      <c r="A376" s="22"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -10263,7 +10390,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="21"/>
+      <c r="A377" s="22"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -10285,7 +10412,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="21"/>
+      <c r="A378" s="22"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -10307,7 +10434,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="21"/>
+      <c r="A379" s="22"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -10329,7 +10456,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="21"/>
+      <c r="A380" s="22"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -10351,7 +10478,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="21"/>
+      <c r="A381" s="22"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -10373,7 +10500,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="21"/>
+      <c r="A382" s="22"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -10395,7 +10522,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="21"/>
+      <c r="A383" s="22"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -10417,7 +10544,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="21"/>
+      <c r="A384" s="22"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -10439,7 +10566,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="21"/>
+      <c r="A385" s="22"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -10461,7 +10588,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="21"/>
+      <c r="A386" s="22"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -10483,7 +10610,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="21"/>
+      <c r="A387" s="22"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -10505,7 +10632,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="21"/>
+      <c r="A388" s="22"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -10527,7 +10654,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="21"/>
+      <c r="A389" s="22"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -10549,7 +10676,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="21"/>
+      <c r="A390" s="22"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -10571,7 +10698,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="21"/>
+      <c r="A391" s="22"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -10593,7 +10720,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="21"/>
+      <c r="A392" s="22"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -10615,7 +10742,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="21"/>
+      <c r="A393" s="22"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -10637,7 +10764,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="21"/>
+      <c r="A394" s="22"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -10659,7 +10786,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="21"/>
+      <c r="A395" s="22"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -10681,7 +10808,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="21"/>
+      <c r="A396" s="22"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -10703,7 +10830,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="21"/>
+      <c r="A397" s="22"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -10725,7 +10852,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="21"/>
+      <c r="A398" s="22"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -10747,7 +10874,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="21"/>
+      <c r="A399" s="22"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -10769,7 +10896,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="21"/>
+      <c r="A400" s="22"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -10791,7 +10918,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="21"/>
+      <c r="A401" s="22"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>
@@ -10827,27 +10954,27 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K30 K46:K401" type="list">
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="between" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K30 K48:K401" type="list">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L30 L46:L401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L30 L44:L401" type="list">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M30 M46:M401" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M6:M30 M48:M401" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="equal" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K31:K45" type="list">
+    <dataValidation allowBlank="true" error="Please choose a value from the dropdown list." errorStyle="stop" operator="equal" prompt="Select today's overall feeling" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K31:K47" type="list">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L31:L45" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's satisfaction level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L31:L43" type="list">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M31:M45" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Select today's energy level" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M31:M47" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="104">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   <si>
     <t xml:space="preserve">Good day</t>
   </si>
+  <si>
+    <t xml:space="preserve">makeup class </t>
+  </si>
 </sst>
 </file>
 
@@ -341,7 +344,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,12 +459,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -532,7 +529,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -614,10 +611,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3101,7 +3094,7 @@
       <c r="M46" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="N46" s="21" t="s">
+      <c r="N46" s="17" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3152,29 +3145,53 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="22"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="12" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I48" s="15" t="n">
         <f aca="false">IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J48" s="15" t="n">
         <f aca="false">IF(I48="","",1440-I48)</f>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="22"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -3196,7 +3213,7 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="22"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -3218,7 +3235,7 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -3240,7 +3257,7 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -3262,7 +3279,7 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -3284,7 +3301,7 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -3306,7 +3323,7 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -3328,7 +3345,7 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="22"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3350,7 +3367,7 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="22"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -3372,7 +3389,7 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="22"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -3394,7 +3411,7 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -3416,7 +3433,7 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3438,7 +3455,7 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="22"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3460,7 +3477,7 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="22"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3482,7 +3499,7 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="22"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3504,7 +3521,7 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3526,7 +3543,7 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3548,7 +3565,7 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22"/>
+      <c r="A66" s="21"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3570,7 +3587,7 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="22"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3592,7 +3609,7 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="22"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3614,7 +3631,7 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3636,7 +3653,7 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="22"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3658,7 +3675,7 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="22"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3680,7 +3697,7 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="22"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3702,7 +3719,7 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="22"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3724,7 +3741,7 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="22"/>
+      <c r="A74" s="21"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3746,7 +3763,7 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="22"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3768,7 +3785,7 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="22"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3790,7 +3807,7 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="22"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3812,7 +3829,7 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="22"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3834,7 +3851,7 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="22"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3856,7 +3873,7 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="22"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3878,7 +3895,7 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="22"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3900,7 +3917,7 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="22"/>
+      <c r="A82" s="21"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3922,7 +3939,7 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="22"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -3944,7 +3961,7 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="22"/>
+      <c r="A84" s="21"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -3966,7 +3983,7 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="22"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -3988,7 +4005,7 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="22"/>
+      <c r="A86" s="21"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -4010,7 +4027,7 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="22"/>
+      <c r="A87" s="21"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -4032,7 +4049,7 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="22"/>
+      <c r="A88" s="21"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -4054,7 +4071,7 @@
       <c r="N88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="22"/>
+      <c r="A89" s="21"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -4076,7 +4093,7 @@
       <c r="N89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="22"/>
+      <c r="A90" s="21"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -4098,7 +4115,7 @@
       <c r="N90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="22"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -4120,7 +4137,7 @@
       <c r="N91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="22"/>
+      <c r="A92" s="21"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -4142,7 +4159,7 @@
       <c r="N92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="22"/>
+      <c r="A93" s="21"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -4164,7 +4181,7 @@
       <c r="N93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="22"/>
+      <c r="A94" s="21"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -4186,7 +4203,7 @@
       <c r="N94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="22"/>
+      <c r="A95" s="21"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -4208,7 +4225,7 @@
       <c r="N95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="22"/>
+      <c r="A96" s="21"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -4230,7 +4247,7 @@
       <c r="N96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="22"/>
+      <c r="A97" s="21"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -4252,7 +4269,7 @@
       <c r="N97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="22"/>
+      <c r="A98" s="21"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -4274,7 +4291,7 @@
       <c r="N98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="22"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -4296,7 +4313,7 @@
       <c r="N99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="22"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -4318,7 +4335,7 @@
       <c r="N100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="22"/>
+      <c r="A101" s="21"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
@@ -4340,7 +4357,7 @@
       <c r="N101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="22"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
@@ -4362,7 +4379,7 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="22"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
@@ -4384,7 +4401,7 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="22"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
@@ -4406,7 +4423,7 @@
       <c r="N104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="22"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
@@ -4428,7 +4445,7 @@
       <c r="N105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="22"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
@@ -4450,7 +4467,7 @@
       <c r="N106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="22"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -4472,7 +4489,7 @@
       <c r="N107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="22"/>
+      <c r="A108" s="21"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -4494,7 +4511,7 @@
       <c r="N108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="22"/>
+      <c r="A109" s="21"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -4516,7 +4533,7 @@
       <c r="N109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="22"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -4538,7 +4555,7 @@
       <c r="N110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="22"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -4560,7 +4577,7 @@
       <c r="N111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="22"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -4582,7 +4599,7 @@
       <c r="N112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="22"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -4604,7 +4621,7 @@
       <c r="N113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="22"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -4626,7 +4643,7 @@
       <c r="N114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="22"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4648,7 +4665,7 @@
       <c r="N115" s="17"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="22"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4670,7 +4687,7 @@
       <c r="N116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="22"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4692,7 +4709,7 @@
       <c r="N117" s="17"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="22"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4714,7 +4731,7 @@
       <c r="N118" s="17"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="22"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
@@ -4736,7 +4753,7 @@
       <c r="N119" s="17"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="22"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
@@ -4758,7 +4775,7 @@
       <c r="N120" s="17"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="22"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
@@ -4780,7 +4797,7 @@
       <c r="N121" s="17"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="22"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
@@ -4802,7 +4819,7 @@
       <c r="N122" s="17"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="22"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
@@ -4824,7 +4841,7 @@
       <c r="N123" s="17"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="22"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
@@ -4846,7 +4863,7 @@
       <c r="N124" s="17"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="22"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
@@ -4868,7 +4885,7 @@
       <c r="N125" s="17"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="22"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4890,7 +4907,7 @@
       <c r="N126" s="17"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="22"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4912,7 +4929,7 @@
       <c r="N127" s="17"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="22"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4934,7 +4951,7 @@
       <c r="N128" s="17"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="22"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4956,7 +4973,7 @@
       <c r="N129" s="17"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="22"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4978,7 +4995,7 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="22"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -5000,7 +5017,7 @@
       <c r="N131" s="17"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="22"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -5022,7 +5039,7 @@
       <c r="N132" s="17"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="22"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -5044,7 +5061,7 @@
       <c r="N133" s="17"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="22"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
@@ -5066,7 +5083,7 @@
       <c r="N134" s="17"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="22"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
@@ -5088,7 +5105,7 @@
       <c r="N135" s="17"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="22"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
@@ -5110,7 +5127,7 @@
       <c r="N136" s="17"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="22"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -5132,7 +5149,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="22"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -5154,7 +5171,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="22"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -5176,7 +5193,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="22"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -5198,7 +5215,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="22"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -5220,7 +5237,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="22"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -5242,7 +5259,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="22"/>
+      <c r="A143" s="21"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -5264,7 +5281,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="22"/>
+      <c r="A144" s="21"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -5286,7 +5303,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="22"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -5308,7 +5325,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="22"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -5330,7 +5347,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="22"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -5352,7 +5369,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="22"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -5374,7 +5391,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="22"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -5396,7 +5413,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="22"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -5418,7 +5435,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="22"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -5440,7 +5457,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="22"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -5462,7 +5479,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="22"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -5484,7 +5501,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="22"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -5506,7 +5523,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="22"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -5528,7 +5545,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="22"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -5550,7 +5567,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="22"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -5572,7 +5589,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="22"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -5594,7 +5611,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="22"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -5616,7 +5633,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="22"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -5638,7 +5655,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="22"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -5660,7 +5677,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="22"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -5682,7 +5699,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="22"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -5704,7 +5721,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="22"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -5726,7 +5743,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="22"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -5748,7 +5765,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="22"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5770,7 +5787,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="22"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5792,7 +5809,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="22"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5814,7 +5831,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="22"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5836,7 +5853,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="22"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5858,7 +5875,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="22"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5880,7 +5897,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="22"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -5902,7 +5919,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="22"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5924,7 +5941,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="22"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5946,7 +5963,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="22"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5968,7 +5985,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="22"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5990,7 +6007,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="22"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -6012,7 +6029,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="22"/>
+      <c r="A178" s="21"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -6034,7 +6051,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="22"/>
+      <c r="A179" s="21"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -6056,7 +6073,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="22"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -6078,7 +6095,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="22"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -6100,7 +6117,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="22"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -6122,7 +6139,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="22"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -6144,7 +6161,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="22"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -6166,7 +6183,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="22"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -6188,7 +6205,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="22"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -6210,7 +6227,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="22"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -6232,7 +6249,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="22"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -6254,7 +6271,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="22"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -6276,7 +6293,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="22"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -6298,7 +6315,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="22"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -6320,7 +6337,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="22"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -6342,7 +6359,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="22"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -6364,7 +6381,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="22"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -6386,7 +6403,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="22"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -6408,7 +6425,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="22"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -6430,7 +6447,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="22"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -6452,7 +6469,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="22"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -6474,7 +6491,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="22"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -6496,7 +6513,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="22"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -6518,7 +6535,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="22"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -6540,7 +6557,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="22"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -6562,7 +6579,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="22"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -6584,7 +6601,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="22"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -6606,7 +6623,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="22"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -6628,7 +6645,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="22"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -6650,7 +6667,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="22"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -6672,7 +6689,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="22"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -6694,7 +6711,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="22"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -6716,7 +6733,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="22"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -6738,7 +6755,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="22"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>
@@ -6760,7 +6777,7 @@
       <c r="N211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="22"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -6782,7 +6799,7 @@
       <c r="N212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="22"/>
+      <c r="A213" s="21"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -6804,7 +6821,7 @@
       <c r="N213" s="17"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="22"/>
+      <c r="A214" s="21"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -6826,7 +6843,7 @@
       <c r="N214" s="17"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="22"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
       <c r="D215" s="14"/>
@@ -6848,7 +6865,7 @@
       <c r="N215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="22"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
       <c r="D216" s="14"/>
@@ -6870,7 +6887,7 @@
       <c r="N216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="22"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
       <c r="D217" s="14"/>
@@ -6892,7 +6909,7 @@
       <c r="N217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="22"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
       <c r="D218" s="14"/>
@@ -6914,7 +6931,7 @@
       <c r="N218" s="17"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="22"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
       <c r="D219" s="14"/>
@@ -6936,7 +6953,7 @@
       <c r="N219" s="17"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="22"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
@@ -6958,7 +6975,7 @@
       <c r="N220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="22"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
@@ -6980,7 +6997,7 @@
       <c r="N221" s="17"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="22"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -7002,7 +7019,7 @@
       <c r="N222" s="17"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="22"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -7024,7 +7041,7 @@
       <c r="N223" s="17"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="22"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -7046,7 +7063,7 @@
       <c r="N224" s="17"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="22"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -7068,7 +7085,7 @@
       <c r="N225" s="17"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="22"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -7090,7 +7107,7 @@
       <c r="N226" s="17"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="22"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -7112,7 +7129,7 @@
       <c r="N227" s="17"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="22"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -7134,7 +7151,7 @@
       <c r="N228" s="17"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="22"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -7156,7 +7173,7 @@
       <c r="N229" s="17"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="22"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -7178,7 +7195,7 @@
       <c r="N230" s="17"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="22"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -7200,7 +7217,7 @@
       <c r="N231" s="17"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="22"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -7222,7 +7239,7 @@
       <c r="N232" s="17"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="22"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -7244,7 +7261,7 @@
       <c r="N233" s="17"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="22"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -7266,7 +7283,7 @@
       <c r="N234" s="17"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="22"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -7288,7 +7305,7 @@
       <c r="N235" s="17"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="22"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -7310,7 +7327,7 @@
       <c r="N236" s="17"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="22"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -7332,7 +7349,7 @@
       <c r="N237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="22"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -7354,7 +7371,7 @@
       <c r="N238" s="17"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="22"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -7376,7 +7393,7 @@
       <c r="N239" s="17"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="22"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -7398,7 +7415,7 @@
       <c r="N240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="22"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -7420,7 +7437,7 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="22"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -7442,7 +7459,7 @@
       <c r="N242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="22"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -7464,7 +7481,7 @@
       <c r="N243" s="17"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="22"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -7486,7 +7503,7 @@
       <c r="N244" s="17"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="22"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -7508,7 +7525,7 @@
       <c r="N245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="22"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -7530,7 +7547,7 @@
       <c r="N246" s="17"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="22"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -7552,7 +7569,7 @@
       <c r="N247" s="17"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="22"/>
+      <c r="A248" s="21"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -7574,7 +7591,7 @@
       <c r="N248" s="17"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="22"/>
+      <c r="A249" s="21"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -7596,7 +7613,7 @@
       <c r="N249" s="17"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="22"/>
+      <c r="A250" s="21"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -7618,7 +7635,7 @@
       <c r="N250" s="17"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="22"/>
+      <c r="A251" s="21"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -7640,7 +7657,7 @@
       <c r="N251" s="17"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="22"/>
+      <c r="A252" s="21"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -7662,7 +7679,7 @@
       <c r="N252" s="17"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="22"/>
+      <c r="A253" s="21"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -7684,7 +7701,7 @@
       <c r="N253" s="17"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="22"/>
+      <c r="A254" s="21"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -7706,7 +7723,7 @@
       <c r="N254" s="17"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="22"/>
+      <c r="A255" s="21"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -7728,7 +7745,7 @@
       <c r="N255" s="17"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="22"/>
+      <c r="A256" s="21"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -7750,7 +7767,7 @@
       <c r="N256" s="17"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="22"/>
+      <c r="A257" s="21"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -7772,7 +7789,7 @@
       <c r="N257" s="17"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="22"/>
+      <c r="A258" s="21"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
       <c r="D258" s="14"/>
@@ -7794,7 +7811,7 @@
       <c r="N258" s="17"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="22"/>
+      <c r="A259" s="21"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
       <c r="D259" s="14"/>
@@ -7816,7 +7833,7 @@
       <c r="N259" s="17"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="22"/>
+      <c r="A260" s="21"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
       <c r="D260" s="14"/>
@@ -7838,7 +7855,7 @@
       <c r="N260" s="17"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="22"/>
+      <c r="A261" s="21"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
       <c r="D261" s="14"/>
@@ -7860,7 +7877,7 @@
       <c r="N261" s="17"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="22"/>
+      <c r="A262" s="21"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
       <c r="D262" s="14"/>
@@ -7882,7 +7899,7 @@
       <c r="N262" s="17"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="22"/>
+      <c r="A263" s="21"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
       <c r="D263" s="14"/>
@@ -7904,7 +7921,7 @@
       <c r="N263" s="17"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="22"/>
+      <c r="A264" s="21"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
       <c r="D264" s="14"/>
@@ -7926,7 +7943,7 @@
       <c r="N264" s="17"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="22"/>
+      <c r="A265" s="21"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
       <c r="D265" s="14"/>
@@ -7948,7 +7965,7 @@
       <c r="N265" s="17"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="22"/>
+      <c r="A266" s="21"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
       <c r="D266" s="14"/>
@@ -7970,7 +7987,7 @@
       <c r="N266" s="17"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="22"/>
+      <c r="A267" s="21"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
       <c r="D267" s="14"/>
@@ -7992,7 +8009,7 @@
       <c r="N267" s="17"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="22"/>
+      <c r="A268" s="21"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
       <c r="D268" s="14"/>
@@ -8014,7 +8031,7 @@
       <c r="N268" s="17"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="22"/>
+      <c r="A269" s="21"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
       <c r="D269" s="14"/>
@@ -8036,7 +8053,7 @@
       <c r="N269" s="17"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="22"/>
+      <c r="A270" s="21"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
@@ -8058,7 +8075,7 @@
       <c r="N270" s="17"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="22"/>
+      <c r="A271" s="21"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
       <c r="D271" s="14"/>
@@ -8080,7 +8097,7 @@
       <c r="N271" s="17"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="22"/>
+      <c r="A272" s="21"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
       <c r="D272" s="14"/>
@@ -8102,7 +8119,7 @@
       <c r="N272" s="17"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="22"/>
+      <c r="A273" s="21"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
       <c r="D273" s="14"/>
@@ -8124,7 +8141,7 @@
       <c r="N273" s="17"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="22"/>
+      <c r="A274" s="21"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
       <c r="D274" s="14"/>
@@ -8146,7 +8163,7 @@
       <c r="N274" s="17"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="22"/>
+      <c r="A275" s="21"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
       <c r="D275" s="14"/>
@@ -8168,7 +8185,7 @@
       <c r="N275" s="17"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="22"/>
+      <c r="A276" s="21"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
       <c r="D276" s="14"/>
@@ -8190,7 +8207,7 @@
       <c r="N276" s="17"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="22"/>
+      <c r="A277" s="21"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
       <c r="D277" s="14"/>
@@ -8212,7 +8229,7 @@
       <c r="N277" s="17"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="22"/>
+      <c r="A278" s="21"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
       <c r="D278" s="14"/>
@@ -8234,7 +8251,7 @@
       <c r="N278" s="17"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="22"/>
+      <c r="A279" s="21"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
       <c r="D279" s="14"/>
@@ -8256,7 +8273,7 @@
       <c r="N279" s="17"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="22"/>
+      <c r="A280" s="21"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
       <c r="D280" s="14"/>
@@ -8278,7 +8295,7 @@
       <c r="N280" s="17"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="22"/>
+      <c r="A281" s="21"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
@@ -8300,7 +8317,7 @@
       <c r="N281" s="17"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="22"/>
+      <c r="A282" s="21"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
       <c r="D282" s="14"/>
@@ -8322,7 +8339,7 @@
       <c r="N282" s="17"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="22"/>
+      <c r="A283" s="21"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
       <c r="D283" s="14"/>
@@ -8344,7 +8361,7 @@
       <c r="N283" s="17"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="22"/>
+      <c r="A284" s="21"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
       <c r="D284" s="14"/>
@@ -8366,7 +8383,7 @@
       <c r="N284" s="17"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="22"/>
+      <c r="A285" s="21"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
       <c r="D285" s="14"/>
@@ -8388,7 +8405,7 @@
       <c r="N285" s="17"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="22"/>
+      <c r="A286" s="21"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
       <c r="D286" s="14"/>
@@ -8410,7 +8427,7 @@
       <c r="N286" s="17"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="22"/>
+      <c r="A287" s="21"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
       <c r="D287" s="14"/>
@@ -8432,7 +8449,7 @@
       <c r="N287" s="17"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="22"/>
+      <c r="A288" s="21"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
       <c r="D288" s="14"/>
@@ -8454,7 +8471,7 @@
       <c r="N288" s="17"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="22"/>
+      <c r="A289" s="21"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
       <c r="D289" s="14"/>
@@ -8476,7 +8493,7 @@
       <c r="N289" s="17"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="22"/>
+      <c r="A290" s="21"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
       <c r="D290" s="14"/>
@@ -8498,7 +8515,7 @@
       <c r="N290" s="17"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="22"/>
+      <c r="A291" s="21"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
       <c r="D291" s="14"/>
@@ -8520,7 +8537,7 @@
       <c r="N291" s="17"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="22"/>
+      <c r="A292" s="21"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
       <c r="D292" s="14"/>
@@ -8542,7 +8559,7 @@
       <c r="N292" s="17"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="22"/>
+      <c r="A293" s="21"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
       <c r="D293" s="14"/>
@@ -8564,7 +8581,7 @@
       <c r="N293" s="17"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="22"/>
+      <c r="A294" s="21"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
       <c r="D294" s="14"/>
@@ -8586,7 +8603,7 @@
       <c r="N294" s="17"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="22"/>
+      <c r="A295" s="21"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
       <c r="D295" s="14"/>
@@ -8608,7 +8625,7 @@
       <c r="N295" s="17"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="22"/>
+      <c r="A296" s="21"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
       <c r="D296" s="14"/>
@@ -8630,7 +8647,7 @@
       <c r="N296" s="17"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="22"/>
+      <c r="A297" s="21"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
       <c r="D297" s="14"/>
@@ -8652,7 +8669,7 @@
       <c r="N297" s="17"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="22"/>
+      <c r="A298" s="21"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
       <c r="D298" s="14"/>
@@ -8674,7 +8691,7 @@
       <c r="N298" s="17"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="22"/>
+      <c r="A299" s="21"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
       <c r="D299" s="14"/>
@@ -8696,7 +8713,7 @@
       <c r="N299" s="17"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="22"/>
+      <c r="A300" s="21"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
       <c r="D300" s="14"/>
@@ -8718,7 +8735,7 @@
       <c r="N300" s="17"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="22"/>
+      <c r="A301" s="21"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
       <c r="D301" s="14"/>
@@ -8740,7 +8757,7 @@
       <c r="N301" s="17"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="22"/>
+      <c r="A302" s="21"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
       <c r="D302" s="14"/>
@@ -8762,7 +8779,7 @@
       <c r="N302" s="17"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="22"/>
+      <c r="A303" s="21"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
       <c r="D303" s="14"/>
@@ -8784,7 +8801,7 @@
       <c r="N303" s="17"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="22"/>
+      <c r="A304" s="21"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
       <c r="D304" s="14"/>
@@ -8806,7 +8823,7 @@
       <c r="N304" s="17"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="22"/>
+      <c r="A305" s="21"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
       <c r="D305" s="14"/>
@@ -8828,7 +8845,7 @@
       <c r="N305" s="17"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="22"/>
+      <c r="A306" s="21"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
       <c r="D306" s="14"/>
@@ -8850,7 +8867,7 @@
       <c r="N306" s="17"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="22"/>
+      <c r="A307" s="21"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
       <c r="D307" s="14"/>
@@ -8872,7 +8889,7 @@
       <c r="N307" s="17"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="22"/>
+      <c r="A308" s="21"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
       <c r="D308" s="14"/>
@@ -8894,7 +8911,7 @@
       <c r="N308" s="17"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="22"/>
+      <c r="A309" s="21"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
       <c r="D309" s="14"/>
@@ -8916,7 +8933,7 @@
       <c r="N309" s="17"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="22"/>
+      <c r="A310" s="21"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
       <c r="D310" s="14"/>
@@ -8938,7 +8955,7 @@
       <c r="N310" s="17"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="22"/>
+      <c r="A311" s="21"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
       <c r="D311" s="14"/>
@@ -8960,7 +8977,7 @@
       <c r="N311" s="17"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="22"/>
+      <c r="A312" s="21"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
       <c r="D312" s="14"/>
@@ -8982,7 +8999,7 @@
       <c r="N312" s="17"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="22"/>
+      <c r="A313" s="21"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
       <c r="D313" s="14"/>
@@ -9004,7 +9021,7 @@
       <c r="N313" s="17"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="22"/>
+      <c r="A314" s="21"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
       <c r="D314" s="14"/>
@@ -9026,7 +9043,7 @@
       <c r="N314" s="17"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="22"/>
+      <c r="A315" s="21"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
       <c r="D315" s="14"/>
@@ -9048,7 +9065,7 @@
       <c r="N315" s="17"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="22"/>
+      <c r="A316" s="21"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
       <c r="D316" s="14"/>
@@ -9070,7 +9087,7 @@
       <c r="N316" s="17"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="22"/>
+      <c r="A317" s="21"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
       <c r="D317" s="14"/>
@@ -9092,7 +9109,7 @@
       <c r="N317" s="17"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="22"/>
+      <c r="A318" s="21"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
       <c r="D318" s="14"/>
@@ -9114,7 +9131,7 @@
       <c r="N318" s="17"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="22"/>
+      <c r="A319" s="21"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
       <c r="D319" s="14"/>
@@ -9136,7 +9153,7 @@
       <c r="N319" s="17"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="22"/>
+      <c r="A320" s="21"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
       <c r="D320" s="14"/>
@@ -9158,7 +9175,7 @@
       <c r="N320" s="17"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="22"/>
+      <c r="A321" s="21"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
       <c r="D321" s="14"/>
@@ -9180,7 +9197,7 @@
       <c r="N321" s="17"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="22"/>
+      <c r="A322" s="21"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
       <c r="D322" s="14"/>
@@ -9202,7 +9219,7 @@
       <c r="N322" s="17"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="22"/>
+      <c r="A323" s="21"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
       <c r="D323" s="14"/>
@@ -9224,7 +9241,7 @@
       <c r="N323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="22"/>
+      <c r="A324" s="21"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
       <c r="D324" s="14"/>
@@ -9246,7 +9263,7 @@
       <c r="N324" s="17"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="22"/>
+      <c r="A325" s="21"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
       <c r="D325" s="14"/>
@@ -9268,7 +9285,7 @@
       <c r="N325" s="17"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="22"/>
+      <c r="A326" s="21"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
       <c r="D326" s="14"/>
@@ -9290,7 +9307,7 @@
       <c r="N326" s="17"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="22"/>
+      <c r="A327" s="21"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
       <c r="D327" s="14"/>
@@ -9312,7 +9329,7 @@
       <c r="N327" s="17"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="22"/>
+      <c r="A328" s="21"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
       <c r="D328" s="14"/>
@@ -9334,7 +9351,7 @@
       <c r="N328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="22"/>
+      <c r="A329" s="21"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
       <c r="D329" s="14"/>
@@ -9356,7 +9373,7 @@
       <c r="N329" s="17"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="22"/>
+      <c r="A330" s="21"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
       <c r="D330" s="14"/>
@@ -9378,7 +9395,7 @@
       <c r="N330" s="17"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="22"/>
+      <c r="A331" s="21"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
       <c r="D331" s="14"/>
@@ -9400,7 +9417,7 @@
       <c r="N331" s="17"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="22"/>
+      <c r="A332" s="21"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
       <c r="D332" s="14"/>
@@ -9422,7 +9439,7 @@
       <c r="N332" s="17"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="22"/>
+      <c r="A333" s="21"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
       <c r="D333" s="14"/>
@@ -9444,7 +9461,7 @@
       <c r="N333" s="17"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="22"/>
+      <c r="A334" s="21"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
       <c r="D334" s="14"/>
@@ -9466,7 +9483,7 @@
       <c r="N334" s="17"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="22"/>
+      <c r="A335" s="21"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
       <c r="D335" s="14"/>
@@ -9488,7 +9505,7 @@
       <c r="N335" s="17"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="22"/>
+      <c r="A336" s="21"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
       <c r="D336" s="14"/>
@@ -9510,7 +9527,7 @@
       <c r="N336" s="17"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="22"/>
+      <c r="A337" s="21"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
       <c r="D337" s="14"/>
@@ -9532,7 +9549,7 @@
       <c r="N337" s="17"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="22"/>
+      <c r="A338" s="21"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
       <c r="D338" s="14"/>
@@ -9554,7 +9571,7 @@
       <c r="N338" s="17"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="22"/>
+      <c r="A339" s="21"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
       <c r="D339" s="14"/>
@@ -9576,7 +9593,7 @@
       <c r="N339" s="17"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="22"/>
+      <c r="A340" s="21"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
       <c r="D340" s="14"/>
@@ -9598,7 +9615,7 @@
       <c r="N340" s="17"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="22"/>
+      <c r="A341" s="21"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
       <c r="D341" s="14"/>
@@ -9620,7 +9637,7 @@
       <c r="N341" s="17"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="22"/>
+      <c r="A342" s="21"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
       <c r="D342" s="14"/>
@@ -9642,7 +9659,7 @@
       <c r="N342" s="17"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="22"/>
+      <c r="A343" s="21"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
       <c r="D343" s="14"/>
@@ -9664,7 +9681,7 @@
       <c r="N343" s="17"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="22"/>
+      <c r="A344" s="21"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
       <c r="D344" s="14"/>
@@ -9686,7 +9703,7 @@
       <c r="N344" s="17"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="22"/>
+      <c r="A345" s="21"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
       <c r="D345" s="14"/>
@@ -9708,7 +9725,7 @@
       <c r="N345" s="17"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="22"/>
+      <c r="A346" s="21"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
       <c r="D346" s="14"/>
@@ -9730,7 +9747,7 @@
       <c r="N346" s="17"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="22"/>
+      <c r="A347" s="21"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
       <c r="D347" s="14"/>
@@ -9752,7 +9769,7 @@
       <c r="N347" s="17"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="22"/>
+      <c r="A348" s="21"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
       <c r="D348" s="14"/>
@@ -9774,7 +9791,7 @@
       <c r="N348" s="17"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="22"/>
+      <c r="A349" s="21"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
       <c r="D349" s="14"/>
@@ -9796,7 +9813,7 @@
       <c r="N349" s="17"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="22"/>
+      <c r="A350" s="21"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
       <c r="D350" s="14"/>
@@ -9818,7 +9835,7 @@
       <c r="N350" s="17"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="22"/>
+      <c r="A351" s="21"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
       <c r="D351" s="14"/>
@@ -9840,7 +9857,7 @@
       <c r="N351" s="17"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="22"/>
+      <c r="A352" s="21"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
       <c r="D352" s="14"/>
@@ -9862,7 +9879,7 @@
       <c r="N352" s="17"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="22"/>
+      <c r="A353" s="21"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
       <c r="D353" s="14"/>
@@ -9884,7 +9901,7 @@
       <c r="N353" s="17"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="22"/>
+      <c r="A354" s="21"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
       <c r="D354" s="14"/>
@@ -9906,7 +9923,7 @@
       <c r="N354" s="17"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="22"/>
+      <c r="A355" s="21"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
       <c r="D355" s="14"/>
@@ -9928,7 +9945,7 @@
       <c r="N355" s="17"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="22"/>
+      <c r="A356" s="21"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
       <c r="D356" s="14"/>
@@ -9950,7 +9967,7 @@
       <c r="N356" s="17"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="22"/>
+      <c r="A357" s="21"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
       <c r="D357" s="14"/>
@@ -9972,7 +9989,7 @@
       <c r="N357" s="17"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="22"/>
+      <c r="A358" s="21"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
       <c r="D358" s="14"/>
@@ -9994,7 +10011,7 @@
       <c r="N358" s="17"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="22"/>
+      <c r="A359" s="21"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
       <c r="D359" s="14"/>
@@ -10016,7 +10033,7 @@
       <c r="N359" s="17"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="22"/>
+      <c r="A360" s="21"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
       <c r="D360" s="14"/>
@@ -10038,7 +10055,7 @@
       <c r="N360" s="17"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="22"/>
+      <c r="A361" s="21"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
       <c r="D361" s="14"/>
@@ -10060,7 +10077,7 @@
       <c r="N361" s="17"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="22"/>
+      <c r="A362" s="21"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
       <c r="D362" s="14"/>
@@ -10082,7 +10099,7 @@
       <c r="N362" s="17"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="22"/>
+      <c r="A363" s="21"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
       <c r="D363" s="14"/>
@@ -10104,7 +10121,7 @@
       <c r="N363" s="17"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="22"/>
+      <c r="A364" s="21"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
       <c r="D364" s="14"/>
@@ -10126,7 +10143,7 @@
       <c r="N364" s="17"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="22"/>
+      <c r="A365" s="21"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
       <c r="D365" s="14"/>
@@ -10148,7 +10165,7 @@
       <c r="N365" s="17"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="22"/>
+      <c r="A366" s="21"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
       <c r="D366" s="14"/>
@@ -10170,7 +10187,7 @@
       <c r="N366" s="17"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="22"/>
+      <c r="A367" s="21"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
       <c r="D367" s="14"/>
@@ -10192,7 +10209,7 @@
       <c r="N367" s="17"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="22"/>
+      <c r="A368" s="21"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
       <c r="D368" s="14"/>
@@ -10214,7 +10231,7 @@
       <c r="N368" s="17"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="22"/>
+      <c r="A369" s="21"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
       <c r="D369" s="14"/>
@@ -10236,7 +10253,7 @@
       <c r="N369" s="17"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="22"/>
+      <c r="A370" s="21"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
       <c r="D370" s="14"/>
@@ -10258,7 +10275,7 @@
       <c r="N370" s="17"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="22"/>
+      <c r="A371" s="21"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
       <c r="D371" s="14"/>
@@ -10280,7 +10297,7 @@
       <c r="N371" s="17"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="22"/>
+      <c r="A372" s="21"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
       <c r="D372" s="14"/>
@@ -10302,7 +10319,7 @@
       <c r="N372" s="17"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="22"/>
+      <c r="A373" s="21"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
       <c r="D373" s="14"/>
@@ -10324,7 +10341,7 @@
       <c r="N373" s="17"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="22"/>
+      <c r="A374" s="21"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
       <c r="D374" s="14"/>
@@ -10346,7 +10363,7 @@
       <c r="N374" s="17"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="22"/>
+      <c r="A375" s="21"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
       <c r="D375" s="14"/>
@@ -10368,7 +10385,7 @@
       <c r="N375" s="17"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="22"/>
+      <c r="A376" s="21"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
       <c r="D376" s="14"/>
@@ -10390,7 +10407,7 @@
       <c r="N376" s="17"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="22"/>
+      <c r="A377" s="21"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
       <c r="D377" s="14"/>
@@ -10412,7 +10429,7 @@
       <c r="N377" s="17"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="22"/>
+      <c r="A378" s="21"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
       <c r="D378" s="14"/>
@@ -10434,7 +10451,7 @@
       <c r="N378" s="17"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="22"/>
+      <c r="A379" s="21"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
       <c r="D379" s="14"/>
@@ -10456,7 +10473,7 @@
       <c r="N379" s="17"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="22"/>
+      <c r="A380" s="21"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
       <c r="D380" s="14"/>
@@ -10478,7 +10495,7 @@
       <c r="N380" s="17"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="22"/>
+      <c r="A381" s="21"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
       <c r="D381" s="14"/>
@@ -10500,7 +10517,7 @@
       <c r="N381" s="17"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="22"/>
+      <c r="A382" s="21"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
       <c r="D382" s="14"/>
@@ -10522,7 +10539,7 @@
       <c r="N382" s="17"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="22"/>
+      <c r="A383" s="21"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
       <c r="D383" s="14"/>
@@ -10544,7 +10561,7 @@
       <c r="N383" s="17"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="22"/>
+      <c r="A384" s="21"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
       <c r="D384" s="14"/>
@@ -10566,7 +10583,7 @@
       <c r="N384" s="17"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="22"/>
+      <c r="A385" s="21"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
       <c r="D385" s="14"/>
@@ -10588,7 +10605,7 @@
       <c r="N385" s="17"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="22"/>
+      <c r="A386" s="21"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
       <c r="D386" s="14"/>
@@ -10610,7 +10627,7 @@
       <c r="N386" s="17"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="22"/>
+      <c r="A387" s="21"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
       <c r="D387" s="14"/>
@@ -10632,7 +10649,7 @@
       <c r="N387" s="17"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="22"/>
+      <c r="A388" s="21"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
       <c r="D388" s="14"/>
@@ -10654,7 +10671,7 @@
       <c r="N388" s="17"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="22"/>
+      <c r="A389" s="21"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
       <c r="D389" s="14"/>
@@ -10676,7 +10693,7 @@
       <c r="N389" s="17"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="22"/>
+      <c r="A390" s="21"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
       <c r="D390" s="14"/>
@@ -10698,7 +10715,7 @@
       <c r="N390" s="17"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="22"/>
+      <c r="A391" s="21"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
       <c r="D391" s="14"/>
@@ -10720,7 +10737,7 @@
       <c r="N391" s="17"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="22"/>
+      <c r="A392" s="21"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
       <c r="D392" s="14"/>
@@ -10742,7 +10759,7 @@
       <c r="N392" s="17"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="22"/>
+      <c r="A393" s="21"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
       <c r="D393" s="14"/>
@@ -10764,7 +10781,7 @@
       <c r="N393" s="17"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="22"/>
+      <c r="A394" s="21"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
       <c r="D394" s="14"/>
@@ -10786,7 +10803,7 @@
       <c r="N394" s="17"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="22"/>
+      <c r="A395" s="21"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
       <c r="D395" s="14"/>
@@ -10808,7 +10825,7 @@
       <c r="N395" s="17"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="22"/>
+      <c r="A396" s="21"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
       <c r="D396" s="14"/>
@@ -10830,7 +10847,7 @@
       <c r="N396" s="17"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="22"/>
+      <c r="A397" s="21"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
       <c r="D397" s="14"/>
@@ -10852,7 +10869,7 @@
       <c r="N397" s="17"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="22"/>
+      <c r="A398" s="21"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
       <c r="D398" s="14"/>
@@ -10874,7 +10891,7 @@
       <c r="N398" s="17"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="22"/>
+      <c r="A399" s="21"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
       <c r="D399" s="14"/>
@@ -10896,7 +10913,7 @@
       <c r="N399" s="17"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="22"/>
+      <c r="A400" s="21"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
       <c r="D400" s="14"/>
@@ -10918,7 +10935,7 @@
       <c r="N400" s="17"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="22"/>
+      <c r="A401" s="21"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
       <c r="D401" s="14"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t xml:space="preserve">makeup class </t>
+  </si>
+  <si>
+    <t xml:space="preserve">protest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">home going</t>
   </si>
 </sst>
 </file>
@@ -3191,48 +3197,96 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="12" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I49" s="15" t="n">
         <f aca="false">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J49" s="15" t="n">
         <f aca="false">IF(I49="","",1440-I49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I50" s="15" t="n">
         <f aca="false">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J50" s="15" t="n">
         <f aca="false">IF(I50="","",1440-I50)</f>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>770</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t xml:space="preserve">home going</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning new things</t>
   </si>
 </sst>
 </file>
@@ -3289,26 +3292,50 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I51" s="15" t="n">
         <f aca="false">IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J51" s="15" t="n">
         <f aca="false">IF(I51="","",1440-I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="109">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t xml:space="preserve">learning new things</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trying to maintain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning basics first</t>
   </si>
 </sst>
 </file>
@@ -3338,48 +3344,96 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>480</v>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I52" s="15" t="n">
         <f aca="false">IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J52" s="15" t="n">
         <f aca="false">IF(I52="","",1440-I52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="12" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B53" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="I53" s="15" t="n">
         <f aca="false">IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>722</v>
+      </c>
+      <c r="J53" s="15" t="n">
         <f aca="false">IF(I53="","",1440-I53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>718</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t xml:space="preserve">learning basics first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doing some remaining work</t>
   </si>
 </sst>
 </file>
@@ -3403,7 +3406,7 @@
         <v>90</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-8</v>
+        <v>80</v>
       </c>
       <c r="F53" s="14" t="n">
         <v>0</v>
@@ -3416,11 +3419,11 @@
       </c>
       <c r="I53" s="15" t="n">
         <f aca="false">IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
-        <v>722</v>
+        <v>810</v>
       </c>
       <c r="J53" s="15" t="n">
         <f aca="false">IF(I53="","",1440-I53)</f>
-        <v>718</v>
+        <v>630</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>57</v>
@@ -3436,26 +3439,50 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="12" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I54" s="15" t="n">
         <f aca="false">IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J54" s="15" t="n">
         <f aca="false">IF(I54="","",1440-I54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t xml:space="preserve">doing some remaining work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">going through some stuff</t>
   </si>
 </sst>
 </file>
@@ -3485,26 +3488,50 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="12" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I55" s="15" t="n">
         <f aca="false">IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J55" s="15" t="n">
         <f aca="false">IF(I55="","",1440-I55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="112">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t xml:space="preserve">going through some stuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">online classes</t>
   </si>
 </sst>
 </file>
@@ -3534,26 +3537,50 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="12" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I56" s="15" t="n">
         <f aca="false">IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J56" s="15" t="n">
         <f aca="false">IF(I56="","",1440-I56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="113">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t xml:space="preserve">online classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repo work</t>
   </si>
 </sst>
 </file>
@@ -3583,26 +3586,50 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="12" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="I57" s="15" t="n">
         <f aca="false">IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J57" s="15" t="n">
         <f aca="false">IF(I57="","",1440-I57)</f>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t xml:space="preserve">repo work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all day attending classes </t>
   </si>
 </sst>
 </file>
@@ -3632,26 +3635,50 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="12" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G58" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I58" s="15" t="n">
         <f aca="false">IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J58" s="15" t="n">
         <f aca="false">IF(I58="","",1440-I58)</f>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="117">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -356,13 +356,22 @@
     <t xml:space="preserve">going through some stuff</t>
   </si>
   <si>
-    <t xml:space="preserve">online classes</t>
+    <t xml:space="preserve">codes practice</t>
   </si>
   <si>
     <t xml:space="preserve">repo work</t>
   </si>
   <si>
     <t xml:space="preserve">all day attending classes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">minor project setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repo editing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poster making</t>
   </si>
 </sst>
 </file>
@@ -3559,21 +3568,21 @@
         <v>70</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H56" s="14" t="n">
         <v>90</v>
       </c>
       <c r="I56" s="15" t="n">
         <f aca="false">IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
-        <v>990</v>
+        <v>690</v>
       </c>
       <c r="J56" s="15" t="n">
         <f aca="false">IF(I56="","",1440-I56)</f>
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>57</v>
@@ -3605,21 +3614,21 @@
         <v>100</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H57" s="14" t="n">
         <v>70</v>
       </c>
       <c r="I57" s="15" t="n">
         <f aca="false">IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
-        <v>870</v>
+        <v>970</v>
       </c>
       <c r="J57" s="15" t="n">
         <f aca="false">IF(I57="","",1440-I57)</f>
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>57</v>
@@ -3651,21 +3660,21 @@
         <v>80</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H58" s="14" t="n">
         <v>80</v>
       </c>
       <c r="I58" s="15" t="n">
         <f aca="false">IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
-        <v>1130</v>
+        <v>930</v>
       </c>
       <c r="J58" s="15" t="n">
         <f aca="false">IF(I58="","",1440-I58)</f>
-        <v>310</v>
+        <v>510</v>
       </c>
       <c r="K58" s="16" t="s">
         <v>57</v>
@@ -3681,70 +3690,142 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="12" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="G59" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I59" s="15" t="n">
         <f aca="false">IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J59" s="15" t="n">
         <f aca="false">IF(I59="","",1440-I59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="21"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="12" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G60" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I60" s="15" t="n">
         <f aca="false">IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J60" s="15" t="n">
         <f aca="false">IF(I60="","",1440-I60)</f>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="21"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="12" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I61" s="15" t="n">
         <f aca="false">IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J61" s="15" t="n">
         <f aca="false">IF(I61="","",1440-I61)</f>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="21"/>

--- a/12625267.xlsx
+++ b/12625267.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="119">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -372,6 +372,12 @@
   </si>
   <si>
     <t xml:space="preserve">poster making</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leaving comfort space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relaxing</t>
   </si>
 </sst>
 </file>
@@ -3828,70 +3834,142 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="12" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I62" s="15" t="n">
         <f aca="false">IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J62" s="15" t="n">
         <f aca="false">IF(I62="","",1440-I62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="12" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="I63" s="15" t="n">
         <f aca="false">IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J63" s="15" t="n">
         <f aca="false">IF(I63="","",1440-I63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I64" s="15" t="n">
         <f aca="false">IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J64" s="15" t="n">
         <f aca="false">IF(I64="","",1440-I64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="21"/>
